--- a/Tests/Validation/Wheat/UoM_WheatProject/WaggaWagga2024_Observed.xlsx
+++ b/Tests/Validation/Wheat/UoM_WheatProject/WaggaWagga2024_Observed.xlsx
@@ -2611,7 +2611,9 @@
       <c r="K71"/>
       <c r="L71"/>
       <c r="M71"/>
-      <c r="N71"/>
+      <c r="N71" t="n">
+        <v>1305.67627546936</v>
+      </c>
       <c r="O71"/>
       <c r="P71"/>
       <c r="Q71"/>
@@ -5197,7 +5199,9 @@
       <c r="K164"/>
       <c r="L164"/>
       <c r="M164"/>
-      <c r="N164"/>
+      <c r="N164" t="n">
+        <v>1465.5553361213</v>
+      </c>
       <c r="O164"/>
       <c r="P164"/>
       <c r="Q164"/>
@@ -7781,7 +7785,9 @@
       <c r="K257"/>
       <c r="L257"/>
       <c r="M257"/>
-      <c r="N257"/>
+      <c r="N257" t="n">
+        <v>1218.66045250697</v>
+      </c>
       <c r="O257"/>
       <c r="P257"/>
       <c r="Q257"/>
@@ -10441,7 +10447,9 @@
       <c r="K353"/>
       <c r="L353"/>
       <c r="M353"/>
-      <c r="N353"/>
+      <c r="N353" t="n">
+        <v>1521.59343465952</v>
+      </c>
       <c r="O353"/>
       <c r="P353"/>
       <c r="Q353"/>
@@ -12883,7 +12891,9 @@
       <c r="K441"/>
       <c r="L441"/>
       <c r="M441"/>
-      <c r="N441"/>
+      <c r="N441" t="n">
+        <v>1273.67819164338</v>
+      </c>
       <c r="O441"/>
       <c r="P441"/>
       <c r="Q441"/>
@@ -15521,7 +15531,9 @@
       <c r="K536"/>
       <c r="L536"/>
       <c r="M536"/>
-      <c r="N536"/>
+      <c r="N536" t="n">
+        <v>1224.39899220269</v>
+      </c>
       <c r="O536"/>
       <c r="P536"/>
       <c r="Q536"/>
@@ -18077,7 +18089,9 @@
       <c r="K628"/>
       <c r="L628"/>
       <c r="M628"/>
-      <c r="N628"/>
+      <c r="N628" t="n">
+        <v>1542.14245829462</v>
+      </c>
       <c r="O628"/>
       <c r="P628"/>
       <c r="Q628"/>
@@ -20691,7 +20705,9 @@
       <c r="K722"/>
       <c r="L722"/>
       <c r="M722"/>
-      <c r="N722"/>
+      <c r="N722" t="n">
+        <v>1657.63695091728</v>
+      </c>
       <c r="O722"/>
       <c r="P722"/>
       <c r="Q722"/>
@@ -23361,7 +23377,9 @@
       <c r="K818"/>
       <c r="L818"/>
       <c r="M818"/>
-      <c r="N818"/>
+      <c r="N818" t="n">
+        <v>1613.51014119263</v>
+      </c>
       <c r="O818"/>
       <c r="P818"/>
       <c r="Q818"/>
@@ -25829,7 +25847,9 @@
       <c r="K907"/>
       <c r="L907"/>
       <c r="M907"/>
-      <c r="N907"/>
+      <c r="N907" t="n">
+        <v>1435.83620017844</v>
+      </c>
       <c r="O907"/>
       <c r="P907"/>
       <c r="Q907"/>
@@ -28439,7 +28459,9 @@
       <c r="K1001"/>
       <c r="L1001"/>
       <c r="M1001"/>
-      <c r="N1001"/>
+      <c r="N1001" t="n">
+        <v>1338.14725587298</v>
+      </c>
       <c r="O1001"/>
       <c r="P1001"/>
       <c r="Q1001"/>
@@ -31099,7 +31121,9 @@
       <c r="K1097"/>
       <c r="L1097"/>
       <c r="M1097"/>
-      <c r="N1097"/>
+      <c r="N1097" t="n">
+        <v>1720.93487939496</v>
+      </c>
       <c r="O1097"/>
       <c r="P1097"/>
       <c r="Q1097"/>
@@ -33571,7 +33595,9 @@
       <c r="K1186"/>
       <c r="L1186"/>
       <c r="M1186"/>
-      <c r="N1186"/>
+      <c r="N1186" t="n">
+        <v>1566.94642876349</v>
+      </c>
       <c r="O1186"/>
       <c r="P1186"/>
       <c r="Q1186"/>
@@ -36151,7 +36177,9 @@
       <c r="K1279"/>
       <c r="L1279"/>
       <c r="M1279"/>
-      <c r="N1279"/>
+      <c r="N1279" t="n">
+        <v>1249.55718979385</v>
+      </c>
       <c r="O1279"/>
       <c r="P1279"/>
       <c r="Q1279"/>
@@ -38763,7 +38791,9 @@
       <c r="K1373"/>
       <c r="L1373"/>
       <c r="M1373"/>
-      <c r="N1373"/>
+      <c r="N1373" t="n">
+        <v>1519.14733406093</v>
+      </c>
       <c r="O1373"/>
       <c r="P1373"/>
       <c r="Q1373"/>
@@ -41427,7 +41457,9 @@
       <c r="K1469"/>
       <c r="L1469"/>
       <c r="M1469"/>
-      <c r="N1469"/>
+      <c r="N1469" t="n">
+        <v>1168.07768628824</v>
+      </c>
       <c r="O1469"/>
       <c r="P1469"/>
       <c r="Q1469"/>

--- a/Tests/Validation/Wheat/UoM_WheatProject/WaggaWagga2024_Observed.xlsx
+++ b/Tests/Validation/Wheat/UoM_WheatProject/WaggaWagga2024_Observed.xlsx
@@ -203,6 +203,9 @@
     <t xml:space="preserve">20/11/2024 00:00:00</t>
   </si>
   <si>
+    <t xml:space="preserve">HarvestRipe</t>
+  </si>
+  <si>
     <t xml:space="preserve">09/09/2024 00:00:00</t>
   </si>
   <si>
@@ -357,9 +360,6 @@
   </si>
   <si>
     <t xml:space="preserve">13/08/2024 00:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HarvestRipe</t>
   </si>
 </sst>
 </file>
@@ -19942,7 +19942,9 @@
       <c r="Q690"/>
       <c r="R690"/>
       <c r="S690"/>
-      <c r="T690"/>
+      <c r="T690" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="691">
       <c r="A691" t="s">
@@ -19970,7 +19972,9 @@
       <c r="Q691"/>
       <c r="R691"/>
       <c r="S691"/>
-      <c r="T691"/>
+      <c r="T691" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="692">
       <c r="A692" t="s">
@@ -19998,7 +20002,9 @@
       <c r="Q692"/>
       <c r="R692"/>
       <c r="S692"/>
-      <c r="T692"/>
+      <c r="T692" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="693">
       <c r="A693" t="s">
@@ -20026,7 +20032,9 @@
       <c r="Q693"/>
       <c r="R693"/>
       <c r="S693"/>
-      <c r="T693"/>
+      <c r="T693" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="694">
       <c r="A694" t="s">
@@ -20054,7 +20062,9 @@
       <c r="Q694"/>
       <c r="R694"/>
       <c r="S694"/>
-      <c r="T694"/>
+      <c r="T694" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="695">
       <c r="A695" t="s">
@@ -20082,7 +20092,9 @@
       <c r="Q695"/>
       <c r="R695"/>
       <c r="S695"/>
-      <c r="T695"/>
+      <c r="T695" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="696">
       <c r="A696" t="s">
@@ -20110,7 +20122,9 @@
       <c r="Q696"/>
       <c r="R696"/>
       <c r="S696"/>
-      <c r="T696"/>
+      <c r="T696" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="697">
       <c r="A697" t="s">
@@ -20138,7 +20152,9 @@
       <c r="Q697"/>
       <c r="R697"/>
       <c r="S697"/>
-      <c r="T697"/>
+      <c r="T697" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="698">
       <c r="A698" t="s">
@@ -20166,7 +20182,9 @@
       <c r="Q698"/>
       <c r="R698"/>
       <c r="S698"/>
-      <c r="T698"/>
+      <c r="T698" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="699">
       <c r="A699" t="s">
@@ -20194,7 +20212,9 @@
       <c r="Q699"/>
       <c r="R699"/>
       <c r="S699"/>
-      <c r="T699"/>
+      <c r="T699" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="700">
       <c r="A700" t="s">
@@ -20222,7 +20242,9 @@
       <c r="Q700"/>
       <c r="R700"/>
       <c r="S700"/>
-      <c r="T700"/>
+      <c r="T700" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="701">
       <c r="A701" t="s">
@@ -20250,7 +20272,9 @@
       <c r="Q701"/>
       <c r="R701"/>
       <c r="S701"/>
-      <c r="T701"/>
+      <c r="T701" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="702">
       <c r="A702" t="s">
@@ -20278,7 +20302,9 @@
       <c r="Q702"/>
       <c r="R702"/>
       <c r="S702"/>
-      <c r="T702"/>
+      <c r="T702" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="703">
       <c r="A703" t="s">
@@ -20306,7 +20332,9 @@
       <c r="Q703"/>
       <c r="R703"/>
       <c r="S703"/>
-      <c r="T703"/>
+      <c r="T703" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="704">
       <c r="A704" t="s">
@@ -20334,7 +20362,9 @@
       <c r="Q704"/>
       <c r="R704"/>
       <c r="S704"/>
-      <c r="T704"/>
+      <c r="T704" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="705">
       <c r="A705" t="s">
@@ -20362,7 +20392,9 @@
       <c r="Q705"/>
       <c r="R705"/>
       <c r="S705"/>
-      <c r="T705"/>
+      <c r="T705" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="706">
       <c r="A706" t="s">
@@ -20390,7 +20422,9 @@
       <c r="Q706"/>
       <c r="R706"/>
       <c r="S706"/>
-      <c r="T706"/>
+      <c r="T706" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="707">
       <c r="A707" t="s">
@@ -20418,7 +20452,9 @@
       <c r="Q707"/>
       <c r="R707"/>
       <c r="S707"/>
-      <c r="T707"/>
+      <c r="T707" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="708">
       <c r="A708" t="s">
@@ -20446,7 +20482,9 @@
       <c r="Q708"/>
       <c r="R708"/>
       <c r="S708"/>
-      <c r="T708"/>
+      <c r="T708" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="709">
       <c r="A709" t="s">
@@ -20474,7 +20512,9 @@
       <c r="Q709"/>
       <c r="R709"/>
       <c r="S709"/>
-      <c r="T709"/>
+      <c r="T709" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="710">
       <c r="A710" t="s">
@@ -20502,7 +20542,9 @@
       <c r="Q710"/>
       <c r="R710"/>
       <c r="S710"/>
-      <c r="T710"/>
+      <c r="T710" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="711">
       <c r="A711" t="s">
@@ -20530,7 +20572,9 @@
       <c r="Q711"/>
       <c r="R711"/>
       <c r="S711"/>
-      <c r="T711"/>
+      <c r="T711" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="712">
       <c r="A712" t="s">
@@ -20558,7 +20602,9 @@
       <c r="Q712"/>
       <c r="R712"/>
       <c r="S712"/>
-      <c r="T712"/>
+      <c r="T712" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="713">
       <c r="A713" t="s">
@@ -20586,7 +20632,9 @@
       <c r="Q713"/>
       <c r="R713"/>
       <c r="S713"/>
-      <c r="T713"/>
+      <c r="T713" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="714">
       <c r="A714" t="s">
@@ -20614,7 +20662,9 @@
       <c r="Q714"/>
       <c r="R714"/>
       <c r="S714"/>
-      <c r="T714"/>
+      <c r="T714" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="715">
       <c r="A715" t="s">
@@ -20642,7 +20692,9 @@
       <c r="Q715"/>
       <c r="R715"/>
       <c r="S715"/>
-      <c r="T715"/>
+      <c r="T715" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="716">
       <c r="A716" t="s">
@@ -20670,7 +20722,9 @@
       <c r="Q716"/>
       <c r="R716"/>
       <c r="S716"/>
-      <c r="T716"/>
+      <c r="T716" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="717">
       <c r="A717" t="s">
@@ -20698,7 +20752,9 @@
       <c r="Q717"/>
       <c r="R717"/>
       <c r="S717"/>
-      <c r="T717"/>
+      <c r="T717" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="718">
       <c r="A718" t="s">
@@ -20726,7 +20782,9 @@
       <c r="Q718"/>
       <c r="R718"/>
       <c r="S718"/>
-      <c r="T718"/>
+      <c r="T718" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="719">
       <c r="A719" t="s">
@@ -20754,7 +20812,9 @@
       <c r="Q719"/>
       <c r="R719"/>
       <c r="S719"/>
-      <c r="T719"/>
+      <c r="T719" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="720">
       <c r="A720" t="s">
@@ -20782,7 +20842,9 @@
       <c r="Q720"/>
       <c r="R720"/>
       <c r="S720"/>
-      <c r="T720"/>
+      <c r="T720" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="721">
       <c r="A721" t="s">
@@ -20810,7 +20872,9 @@
       <c r="Q721"/>
       <c r="R721"/>
       <c r="S721"/>
-      <c r="T721"/>
+      <c r="T721" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="722">
       <c r="A722" t="s">
@@ -20838,7 +20902,9 @@
       <c r="Q722"/>
       <c r="R722"/>
       <c r="S722"/>
-      <c r="T722"/>
+      <c r="T722" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="723">
       <c r="A723" t="s">
@@ -20866,7 +20932,9 @@
       <c r="Q723"/>
       <c r="R723"/>
       <c r="S723"/>
-      <c r="T723"/>
+      <c r="T723" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="724">
       <c r="A724" t="s">
@@ -20894,7 +20962,9 @@
       <c r="Q724"/>
       <c r="R724"/>
       <c r="S724"/>
-      <c r="T724"/>
+      <c r="T724" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="725">
       <c r="A725" t="s">
@@ -20922,7 +20992,9 @@
       <c r="Q725"/>
       <c r="R725"/>
       <c r="S725"/>
-      <c r="T725"/>
+      <c r="T725" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="726">
       <c r="A726" t="s">
@@ -20950,7 +21022,9 @@
       <c r="Q726"/>
       <c r="R726"/>
       <c r="S726"/>
-      <c r="T726"/>
+      <c r="T726" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="727">
       <c r="A727" t="s">
@@ -20978,7 +21052,9 @@
       <c r="Q727"/>
       <c r="R727"/>
       <c r="S727"/>
-      <c r="T727"/>
+      <c r="T727" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="728">
       <c r="A728" t="s">
@@ -21006,7 +21082,9 @@
       <c r="Q728"/>
       <c r="R728"/>
       <c r="S728"/>
-      <c r="T728"/>
+      <c r="T728" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="729">
       <c r="A729" t="s">
@@ -21034,7 +21112,9 @@
       <c r="Q729"/>
       <c r="R729"/>
       <c r="S729"/>
-      <c r="T729"/>
+      <c r="T729" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="730">
       <c r="A730" t="s">
@@ -21062,7 +21142,9 @@
       <c r="Q730"/>
       <c r="R730"/>
       <c r="S730"/>
-      <c r="T730"/>
+      <c r="T730" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="731">
       <c r="A731" t="s">
@@ -21090,7 +21172,9 @@
       <c r="Q731"/>
       <c r="R731"/>
       <c r="S731"/>
-      <c r="T731"/>
+      <c r="T731" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="732">
       <c r="A732" t="s">
@@ -21118,7 +21202,9 @@
       <c r="Q732"/>
       <c r="R732"/>
       <c r="S732"/>
-      <c r="T732"/>
+      <c r="T732" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="733">
       <c r="A733" t="s">
@@ -21146,7 +21232,9 @@
       <c r="Q733"/>
       <c r="R733"/>
       <c r="S733"/>
-      <c r="T733"/>
+      <c r="T733" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="734">
       <c r="A734" t="s">
@@ -21174,7 +21262,9 @@
       <c r="Q734"/>
       <c r="R734"/>
       <c r="S734"/>
-      <c r="T734"/>
+      <c r="T734" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="735">
       <c r="A735" t="s">
@@ -21202,7 +21292,9 @@
       <c r="Q735"/>
       <c r="R735"/>
       <c r="S735"/>
-      <c r="T735"/>
+      <c r="T735" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="736">
       <c r="A736" t="s">
@@ -21230,7 +21322,9 @@
       <c r="Q736"/>
       <c r="R736"/>
       <c r="S736"/>
-      <c r="T736"/>
+      <c r="T736" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="737">
       <c r="A737" t="s">
@@ -21258,7 +21352,9 @@
       <c r="Q737"/>
       <c r="R737"/>
       <c r="S737"/>
-      <c r="T737"/>
+      <c r="T737" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="738">
       <c r="A738" t="s">
@@ -21286,7 +21382,9 @@
       <c r="Q738"/>
       <c r="R738"/>
       <c r="S738"/>
-      <c r="T738"/>
+      <c r="T738" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="739">
       <c r="A739" t="s">
@@ -21314,7 +21412,9 @@
       <c r="Q739"/>
       <c r="R739"/>
       <c r="S739"/>
-      <c r="T739"/>
+      <c r="T739" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="740">
       <c r="A740" t="s">
@@ -21342,7 +21442,9 @@
       <c r="Q740"/>
       <c r="R740"/>
       <c r="S740"/>
-      <c r="T740"/>
+      <c r="T740" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="741">
       <c r="A741" t="s">
@@ -21370,7 +21472,9 @@
       <c r="Q741"/>
       <c r="R741"/>
       <c r="S741"/>
-      <c r="T741"/>
+      <c r="T741" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="742">
       <c r="A742" t="s">
@@ -21398,7 +21502,9 @@
       <c r="Q742"/>
       <c r="R742"/>
       <c r="S742"/>
-      <c r="T742"/>
+      <c r="T742" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="743">
       <c r="A743" t="s">
@@ -21426,7 +21532,9 @@
       <c r="Q743"/>
       <c r="R743"/>
       <c r="S743"/>
-      <c r="T743"/>
+      <c r="T743" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="744">
       <c r="A744" t="s">
@@ -21454,7 +21562,9 @@
       <c r="Q744"/>
       <c r="R744"/>
       <c r="S744"/>
-      <c r="T744"/>
+      <c r="T744" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="745">
       <c r="A745" t="s">
@@ -21482,7 +21592,9 @@
       <c r="Q745"/>
       <c r="R745"/>
       <c r="S745"/>
-      <c r="T745"/>
+      <c r="T745" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="746">
       <c r="A746" t="s">
@@ -21510,7 +21622,9 @@
       <c r="Q746"/>
       <c r="R746"/>
       <c r="S746"/>
-      <c r="T746"/>
+      <c r="T746" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="747">
       <c r="A747" t="s">
@@ -21538,7 +21652,9 @@
       <c r="Q747"/>
       <c r="R747"/>
       <c r="S747"/>
-      <c r="T747"/>
+      <c r="T747" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="748">
       <c r="A748" t="s">
@@ -21566,7 +21682,9 @@
       <c r="Q748"/>
       <c r="R748"/>
       <c r="S748"/>
-      <c r="T748"/>
+      <c r="T748" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="749">
       <c r="A749" t="s">
@@ -21594,7 +21712,9 @@
       <c r="Q749"/>
       <c r="R749"/>
       <c r="S749"/>
-      <c r="T749"/>
+      <c r="T749" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="750">
       <c r="A750" t="s">
@@ -21622,7 +21742,9 @@
       <c r="Q750"/>
       <c r="R750"/>
       <c r="S750"/>
-      <c r="T750"/>
+      <c r="T750" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="751">
       <c r="A751" t="s">
@@ -21650,7 +21772,9 @@
       <c r="Q751"/>
       <c r="R751"/>
       <c r="S751"/>
-      <c r="T751"/>
+      <c r="T751" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="752">
       <c r="A752" t="s">
@@ -21678,7 +21802,9 @@
       <c r="Q752"/>
       <c r="R752"/>
       <c r="S752"/>
-      <c r="T752"/>
+      <c r="T752" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="753">
       <c r="A753" t="s">
@@ -21706,14 +21832,16 @@
       <c r="Q753"/>
       <c r="R753"/>
       <c r="S753"/>
-      <c r="T753"/>
+      <c r="T753" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="754">
       <c r="A754" t="s">
         <v>20</v>
       </c>
       <c r="B754" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C754"/>
       <c r="D754"/>
@@ -21767,7 +21895,7 @@
         <v>23</v>
       </c>
       <c r="B756" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C756"/>
       <c r="D756"/>
@@ -21795,7 +21923,7 @@
         <v>24</v>
       </c>
       <c r="B757" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C757"/>
       <c r="D757"/>
@@ -21823,7 +21951,7 @@
         <v>25</v>
       </c>
       <c r="B758" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C758"/>
       <c r="D758"/>
@@ -21877,7 +22005,7 @@
         <v>27</v>
       </c>
       <c r="B760" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C760"/>
       <c r="D760"/>
@@ -21905,7 +22033,7 @@
         <v>28</v>
       </c>
       <c r="B761" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C761"/>
       <c r="D761"/>
@@ -21933,7 +22061,7 @@
         <v>29</v>
       </c>
       <c r="B762" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C762"/>
       <c r="D762"/>
@@ -21961,7 +22089,7 @@
         <v>30</v>
       </c>
       <c r="B763" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C763"/>
       <c r="D763"/>
@@ -21989,7 +22117,7 @@
         <v>31</v>
       </c>
       <c r="B764" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C764"/>
       <c r="D764"/>
@@ -22017,7 +22145,7 @@
         <v>32</v>
       </c>
       <c r="B765" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C765"/>
       <c r="D765"/>
@@ -22045,7 +22173,7 @@
         <v>33</v>
       </c>
       <c r="B766" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C766"/>
       <c r="D766"/>
@@ -22073,7 +22201,7 @@
         <v>34</v>
       </c>
       <c r="B767" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C767"/>
       <c r="D767"/>
@@ -22101,7 +22229,7 @@
         <v>35</v>
       </c>
       <c r="B768" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C768"/>
       <c r="D768"/>
@@ -22157,7 +22285,7 @@
         <v>20</v>
       </c>
       <c r="B770" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C770"/>
       <c r="D770"/>
@@ -22185,7 +22313,7 @@
         <v>22</v>
       </c>
       <c r="B771" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C771"/>
       <c r="D771"/>
@@ -22213,7 +22341,7 @@
         <v>23</v>
       </c>
       <c r="B772" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C772"/>
       <c r="D772"/>
@@ -22241,7 +22369,7 @@
         <v>24</v>
       </c>
       <c r="B773" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C773"/>
       <c r="D773"/>
@@ -22269,7 +22397,7 @@
         <v>25</v>
       </c>
       <c r="B774" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C774"/>
       <c r="D774"/>
@@ -22297,7 +22425,7 @@
         <v>26</v>
       </c>
       <c r="B775" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C775"/>
       <c r="D775"/>
@@ -22325,7 +22453,7 @@
         <v>27</v>
       </c>
       <c r="B776" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C776"/>
       <c r="D776"/>
@@ -22353,7 +22481,7 @@
         <v>28</v>
       </c>
       <c r="B777" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C777"/>
       <c r="D777"/>
@@ -22381,7 +22509,7 @@
         <v>29</v>
       </c>
       <c r="B778" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C778"/>
       <c r="D778"/>
@@ -22409,7 +22537,7 @@
         <v>30</v>
       </c>
       <c r="B779" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C779"/>
       <c r="D779"/>
@@ -22437,7 +22565,7 @@
         <v>31</v>
       </c>
       <c r="B780" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C780"/>
       <c r="D780"/>
@@ -22465,7 +22593,7 @@
         <v>32</v>
       </c>
       <c r="B781" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C781"/>
       <c r="D781"/>
@@ -22493,7 +22621,7 @@
         <v>33</v>
       </c>
       <c r="B782" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C782"/>
       <c r="D782"/>
@@ -22521,7 +22649,7 @@
         <v>34</v>
       </c>
       <c r="B783" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C783"/>
       <c r="D783"/>
@@ -22549,7 +22677,7 @@
         <v>35</v>
       </c>
       <c r="B784" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C784"/>
       <c r="D784"/>
@@ -22577,7 +22705,7 @@
         <v>36</v>
       </c>
       <c r="B785" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C785"/>
       <c r="D785"/>
@@ -22626,7 +22754,9 @@
       <c r="Q786"/>
       <c r="R786"/>
       <c r="S786"/>
-      <c r="T786"/>
+      <c r="T786" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="787">
       <c r="A787" t="s">
@@ -22654,7 +22784,9 @@
       <c r="Q787"/>
       <c r="R787"/>
       <c r="S787"/>
-      <c r="T787"/>
+      <c r="T787" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="788">
       <c r="A788" t="s">
@@ -22682,7 +22814,9 @@
       <c r="Q788"/>
       <c r="R788"/>
       <c r="S788"/>
-      <c r="T788"/>
+      <c r="T788" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="789">
       <c r="A789" t="s">
@@ -22710,7 +22844,9 @@
       <c r="Q789"/>
       <c r="R789"/>
       <c r="S789"/>
-      <c r="T789"/>
+      <c r="T789" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="790">
       <c r="A790" t="s">
@@ -22738,7 +22874,9 @@
       <c r="Q790"/>
       <c r="R790"/>
       <c r="S790"/>
-      <c r="T790"/>
+      <c r="T790" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="791">
       <c r="A791" t="s">
@@ -22766,7 +22904,9 @@
       <c r="Q791"/>
       <c r="R791"/>
       <c r="S791"/>
-      <c r="T791"/>
+      <c r="T791" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="792">
       <c r="A792" t="s">
@@ -22794,7 +22934,9 @@
       <c r="Q792"/>
       <c r="R792"/>
       <c r="S792"/>
-      <c r="T792"/>
+      <c r="T792" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="793">
       <c r="A793" t="s">
@@ -22822,7 +22964,9 @@
       <c r="Q793"/>
       <c r="R793"/>
       <c r="S793"/>
-      <c r="T793"/>
+      <c r="T793" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="794">
       <c r="A794" t="s">
@@ -22850,7 +22994,9 @@
       <c r="Q794"/>
       <c r="R794"/>
       <c r="S794"/>
-      <c r="T794"/>
+      <c r="T794" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="795">
       <c r="A795" t="s">
@@ -22878,7 +23024,9 @@
       <c r="Q795"/>
       <c r="R795"/>
       <c r="S795"/>
-      <c r="T795"/>
+      <c r="T795" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="796">
       <c r="A796" t="s">
@@ -22906,7 +23054,9 @@
       <c r="Q796"/>
       <c r="R796"/>
       <c r="S796"/>
-      <c r="T796"/>
+      <c r="T796" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="797">
       <c r="A797" t="s">
@@ -22934,7 +23084,9 @@
       <c r="Q797"/>
       <c r="R797"/>
       <c r="S797"/>
-      <c r="T797"/>
+      <c r="T797" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="798">
       <c r="A798" t="s">
@@ -22962,7 +23114,9 @@
       <c r="Q798"/>
       <c r="R798"/>
       <c r="S798"/>
-      <c r="T798"/>
+      <c r="T798" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="799">
       <c r="A799" t="s">
@@ -22990,7 +23144,9 @@
       <c r="Q799"/>
       <c r="R799"/>
       <c r="S799"/>
-      <c r="T799"/>
+      <c r="T799" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="800">
       <c r="A800" t="s">
@@ -23018,7 +23174,9 @@
       <c r="Q800"/>
       <c r="R800"/>
       <c r="S800"/>
-      <c r="T800"/>
+      <c r="T800" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="801">
       <c r="A801" t="s">
@@ -23046,14 +23204,16 @@
       <c r="Q801"/>
       <c r="R801"/>
       <c r="S801"/>
-      <c r="T801"/>
+      <c r="T801" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="802">
       <c r="A802" t="s">
         <v>20</v>
       </c>
       <c r="B802" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C802"/>
       <c r="D802"/>
@@ -23107,7 +23267,7 @@
         <v>23</v>
       </c>
       <c r="B804" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C804"/>
       <c r="D804"/>
@@ -23135,7 +23295,7 @@
         <v>24</v>
       </c>
       <c r="B805" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C805"/>
       <c r="D805"/>
@@ -23163,7 +23323,7 @@
         <v>25</v>
       </c>
       <c r="B806" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C806"/>
       <c r="D806"/>
@@ -23217,7 +23377,7 @@
         <v>27</v>
       </c>
       <c r="B808" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C808"/>
       <c r="D808"/>
@@ -23245,7 +23405,7 @@
         <v>28</v>
       </c>
       <c r="B809" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C809"/>
       <c r="D809"/>
@@ -23273,7 +23433,7 @@
         <v>29</v>
       </c>
       <c r="B810" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C810"/>
       <c r="D810"/>
@@ -23301,7 +23461,7 @@
         <v>30</v>
       </c>
       <c r="B811" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C811"/>
       <c r="D811"/>
@@ -23329,7 +23489,7 @@
         <v>31</v>
       </c>
       <c r="B812" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C812"/>
       <c r="D812"/>
@@ -23357,7 +23517,7 @@
         <v>32</v>
       </c>
       <c r="B813" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C813"/>
       <c r="D813"/>
@@ -23385,7 +23545,7 @@
         <v>33</v>
       </c>
       <c r="B814" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C814"/>
       <c r="D814"/>
@@ -23413,7 +23573,7 @@
         <v>34</v>
       </c>
       <c r="B815" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C815"/>
       <c r="D815"/>
@@ -23441,7 +23601,7 @@
         <v>35</v>
       </c>
       <c r="B816" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C816"/>
       <c r="D816"/>
@@ -23497,7 +23657,7 @@
         <v>20</v>
       </c>
       <c r="B818" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C818"/>
       <c r="D818"/>
@@ -23525,7 +23685,7 @@
         <v>22</v>
       </c>
       <c r="B819" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C819"/>
       <c r="D819"/>
@@ -23553,7 +23713,7 @@
         <v>23</v>
       </c>
       <c r="B820" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C820"/>
       <c r="D820"/>
@@ -23581,7 +23741,7 @@
         <v>24</v>
       </c>
       <c r="B821" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C821"/>
       <c r="D821"/>
@@ -23609,7 +23769,7 @@
         <v>25</v>
       </c>
       <c r="B822" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C822"/>
       <c r="D822"/>
@@ -23637,7 +23797,7 @@
         <v>26</v>
       </c>
       <c r="B823" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C823"/>
       <c r="D823"/>
@@ -23665,7 +23825,7 @@
         <v>27</v>
       </c>
       <c r="B824" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C824"/>
       <c r="D824"/>
@@ -23693,7 +23853,7 @@
         <v>28</v>
       </c>
       <c r="B825" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C825"/>
       <c r="D825"/>
@@ -23721,7 +23881,7 @@
         <v>29</v>
       </c>
       <c r="B826" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C826"/>
       <c r="D826"/>
@@ -23749,7 +23909,7 @@
         <v>30</v>
       </c>
       <c r="B827" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C827"/>
       <c r="D827"/>
@@ -23777,7 +23937,7 @@
         <v>31</v>
       </c>
       <c r="B828" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C828"/>
       <c r="D828"/>
@@ -23805,7 +23965,7 @@
         <v>32</v>
       </c>
       <c r="B829" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C829"/>
       <c r="D829"/>
@@ -23833,7 +23993,7 @@
         <v>33</v>
       </c>
       <c r="B830" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C830"/>
       <c r="D830"/>
@@ -23861,7 +24021,7 @@
         <v>34</v>
       </c>
       <c r="B831" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C831"/>
       <c r="D831"/>
@@ -23889,7 +24049,7 @@
         <v>35</v>
       </c>
       <c r="B832" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C832"/>
       <c r="D832"/>
@@ -23917,7 +24077,7 @@
         <v>36</v>
       </c>
       <c r="B833" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C833"/>
       <c r="D833"/>
@@ -23966,7 +24126,9 @@
       <c r="Q834"/>
       <c r="R834"/>
       <c r="S834"/>
-      <c r="T834"/>
+      <c r="T834" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="835">
       <c r="A835" t="s">
@@ -23994,7 +24156,9 @@
       <c r="Q835"/>
       <c r="R835"/>
       <c r="S835"/>
-      <c r="T835"/>
+      <c r="T835" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="836">
       <c r="A836" t="s">
@@ -24022,7 +24186,9 @@
       <c r="Q836"/>
       <c r="R836"/>
       <c r="S836"/>
-      <c r="T836"/>
+      <c r="T836" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="837">
       <c r="A837" t="s">
@@ -24050,7 +24216,9 @@
       <c r="Q837"/>
       <c r="R837"/>
       <c r="S837"/>
-      <c r="T837"/>
+      <c r="T837" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="838">
       <c r="A838" t="s">
@@ -24078,7 +24246,9 @@
       <c r="Q838"/>
       <c r="R838"/>
       <c r="S838"/>
-      <c r="T838"/>
+      <c r="T838" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="839">
       <c r="A839" t="s">
@@ -24106,7 +24276,9 @@
       <c r="Q839"/>
       <c r="R839"/>
       <c r="S839"/>
-      <c r="T839"/>
+      <c r="T839" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="840">
       <c r="A840" t="s">
@@ -24134,7 +24306,9 @@
       <c r="Q840"/>
       <c r="R840"/>
       <c r="S840"/>
-      <c r="T840"/>
+      <c r="T840" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="841">
       <c r="A841" t="s">
@@ -24162,7 +24336,9 @@
       <c r="Q841"/>
       <c r="R841"/>
       <c r="S841"/>
-      <c r="T841"/>
+      <c r="T841" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="842">
       <c r="A842" t="s">
@@ -24190,7 +24366,9 @@
       <c r="Q842"/>
       <c r="R842"/>
       <c r="S842"/>
-      <c r="T842"/>
+      <c r="T842" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="843">
       <c r="A843" t="s">
@@ -24218,7 +24396,9 @@
       <c r="Q843"/>
       <c r="R843"/>
       <c r="S843"/>
-      <c r="T843"/>
+      <c r="T843" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="844">
       <c r="A844" t="s">
@@ -24246,7 +24426,9 @@
       <c r="Q844"/>
       <c r="R844"/>
       <c r="S844"/>
-      <c r="T844"/>
+      <c r="T844" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="845">
       <c r="A845" t="s">
@@ -24274,7 +24456,9 @@
       <c r="Q845"/>
       <c r="R845"/>
       <c r="S845"/>
-      <c r="T845"/>
+      <c r="T845" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="846">
       <c r="A846" t="s">
@@ -24302,7 +24486,9 @@
       <c r="Q846"/>
       <c r="R846"/>
       <c r="S846"/>
-      <c r="T846"/>
+      <c r="T846" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="847">
       <c r="A847" t="s">
@@ -24330,7 +24516,9 @@
       <c r="Q847"/>
       <c r="R847"/>
       <c r="S847"/>
-      <c r="T847"/>
+      <c r="T847" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="848">
       <c r="A848" t="s">
@@ -24358,7 +24546,9 @@
       <c r="Q848"/>
       <c r="R848"/>
       <c r="S848"/>
-      <c r="T848"/>
+      <c r="T848" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="849">
       <c r="A849" t="s">
@@ -24386,14 +24576,16 @@
       <c r="Q849"/>
       <c r="R849"/>
       <c r="S849"/>
-      <c r="T849"/>
+      <c r="T849" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="850">
       <c r="A850" t="s">
         <v>20</v>
       </c>
       <c r="B850" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C850"/>
       <c r="D850"/>
@@ -24447,7 +24639,7 @@
         <v>23</v>
       </c>
       <c r="B852" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C852"/>
       <c r="D852"/>
@@ -24475,7 +24667,7 @@
         <v>24</v>
       </c>
       <c r="B853" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C853"/>
       <c r="D853"/>
@@ -24503,7 +24695,7 @@
         <v>25</v>
       </c>
       <c r="B854" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C854"/>
       <c r="D854"/>
@@ -24557,7 +24749,7 @@
         <v>27</v>
       </c>
       <c r="B856" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C856"/>
       <c r="D856"/>
@@ -24585,7 +24777,7 @@
         <v>28</v>
       </c>
       <c r="B857" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C857"/>
       <c r="D857"/>
@@ -24613,7 +24805,7 @@
         <v>29</v>
       </c>
       <c r="B858" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C858"/>
       <c r="D858"/>
@@ -24641,7 +24833,7 @@
         <v>30</v>
       </c>
       <c r="B859" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C859"/>
       <c r="D859"/>
@@ -24669,7 +24861,7 @@
         <v>31</v>
       </c>
       <c r="B860" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C860"/>
       <c r="D860"/>
@@ -24697,7 +24889,7 @@
         <v>32</v>
       </c>
       <c r="B861" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C861"/>
       <c r="D861"/>
@@ -24725,7 +24917,7 @@
         <v>33</v>
       </c>
       <c r="B862" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C862"/>
       <c r="D862"/>
@@ -24753,7 +24945,7 @@
         <v>34</v>
       </c>
       <c r="B863" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C863"/>
       <c r="D863"/>
@@ -24781,7 +24973,7 @@
         <v>35</v>
       </c>
       <c r="B864" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C864"/>
       <c r="D864"/>
@@ -24837,7 +25029,7 @@
         <v>20</v>
       </c>
       <c r="B866" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C866"/>
       <c r="D866"/>
@@ -24865,7 +25057,7 @@
         <v>22</v>
       </c>
       <c r="B867" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C867"/>
       <c r="D867"/>
@@ -24893,7 +25085,7 @@
         <v>23</v>
       </c>
       <c r="B868" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C868"/>
       <c r="D868"/>
@@ -24921,7 +25113,7 @@
         <v>24</v>
       </c>
       <c r="B869" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C869"/>
       <c r="D869"/>
@@ -24949,7 +25141,7 @@
         <v>25</v>
       </c>
       <c r="B870" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C870"/>
       <c r="D870"/>
@@ -24977,7 +25169,7 @@
         <v>26</v>
       </c>
       <c r="B871" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C871"/>
       <c r="D871"/>
@@ -25005,7 +25197,7 @@
         <v>27</v>
       </c>
       <c r="B872" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C872"/>
       <c r="D872"/>
@@ -25033,7 +25225,7 @@
         <v>28</v>
       </c>
       <c r="B873" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C873"/>
       <c r="D873"/>
@@ -25061,7 +25253,7 @@
         <v>29</v>
       </c>
       <c r="B874" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C874"/>
       <c r="D874"/>
@@ -25089,7 +25281,7 @@
         <v>30</v>
       </c>
       <c r="B875" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C875"/>
       <c r="D875"/>
@@ -25117,7 +25309,7 @@
         <v>31</v>
       </c>
       <c r="B876" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C876"/>
       <c r="D876"/>
@@ -25145,7 +25337,7 @@
         <v>32</v>
       </c>
       <c r="B877" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C877"/>
       <c r="D877"/>
@@ -25173,7 +25365,7 @@
         <v>33</v>
       </c>
       <c r="B878" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C878"/>
       <c r="D878"/>
@@ -25201,7 +25393,7 @@
         <v>34</v>
       </c>
       <c r="B879" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C879"/>
       <c r="D879"/>
@@ -25229,7 +25421,7 @@
         <v>35</v>
       </c>
       <c r="B880" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C880"/>
       <c r="D880"/>
@@ -25257,7 +25449,7 @@
         <v>36</v>
       </c>
       <c r="B881" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C881"/>
       <c r="D881"/>
@@ -25306,7 +25498,9 @@
       <c r="Q882"/>
       <c r="R882"/>
       <c r="S882"/>
-      <c r="T882"/>
+      <c r="T882" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="883">
       <c r="A883" t="s">
@@ -25334,7 +25528,9 @@
       <c r="Q883"/>
       <c r="R883"/>
       <c r="S883"/>
-      <c r="T883"/>
+      <c r="T883" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="884">
       <c r="A884" t="s">
@@ -25362,7 +25558,9 @@
       <c r="Q884"/>
       <c r="R884"/>
       <c r="S884"/>
-      <c r="T884"/>
+      <c r="T884" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="885">
       <c r="A885" t="s">
@@ -25390,7 +25588,9 @@
       <c r="Q885"/>
       <c r="R885"/>
       <c r="S885"/>
-      <c r="T885"/>
+      <c r="T885" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="886">
       <c r="A886" t="s">
@@ -25418,7 +25618,9 @@
       <c r="Q886"/>
       <c r="R886"/>
       <c r="S886"/>
-      <c r="T886"/>
+      <c r="T886" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="887">
       <c r="A887" t="s">
@@ -25446,7 +25648,9 @@
       <c r="Q887"/>
       <c r="R887"/>
       <c r="S887"/>
-      <c r="T887"/>
+      <c r="T887" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="888">
       <c r="A888" t="s">
@@ -25474,7 +25678,9 @@
       <c r="Q888"/>
       <c r="R888"/>
       <c r="S888"/>
-      <c r="T888"/>
+      <c r="T888" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="889">
       <c r="A889" t="s">
@@ -25502,7 +25708,9 @@
       <c r="Q889"/>
       <c r="R889"/>
       <c r="S889"/>
-      <c r="T889"/>
+      <c r="T889" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="890">
       <c r="A890" t="s">
@@ -25530,7 +25738,9 @@
       <c r="Q890"/>
       <c r="R890"/>
       <c r="S890"/>
-      <c r="T890"/>
+      <c r="T890" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="891">
       <c r="A891" t="s">
@@ -25558,7 +25768,9 @@
       <c r="Q891"/>
       <c r="R891"/>
       <c r="S891"/>
-      <c r="T891"/>
+      <c r="T891" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="892">
       <c r="A892" t="s">
@@ -25586,7 +25798,9 @@
       <c r="Q892"/>
       <c r="R892"/>
       <c r="S892"/>
-      <c r="T892"/>
+      <c r="T892" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="893">
       <c r="A893" t="s">
@@ -25614,7 +25828,9 @@
       <c r="Q893"/>
       <c r="R893"/>
       <c r="S893"/>
-      <c r="T893"/>
+      <c r="T893" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="894">
       <c r="A894" t="s">
@@ -25642,7 +25858,9 @@
       <c r="Q894"/>
       <c r="R894"/>
       <c r="S894"/>
-      <c r="T894"/>
+      <c r="T894" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="895">
       <c r="A895" t="s">
@@ -25670,7 +25888,9 @@
       <c r="Q895"/>
       <c r="R895"/>
       <c r="S895"/>
-      <c r="T895"/>
+      <c r="T895" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="896">
       <c r="A896" t="s">
@@ -25698,7 +25918,9 @@
       <c r="Q896"/>
       <c r="R896"/>
       <c r="S896"/>
-      <c r="T896"/>
+      <c r="T896" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="897">
       <c r="A897" t="s">
@@ -25726,14 +25948,16 @@
       <c r="Q897"/>
       <c r="R897"/>
       <c r="S897"/>
-      <c r="T897"/>
+      <c r="T897" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="898">
       <c r="A898" t="s">
         <v>20</v>
       </c>
       <c r="B898" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C898"/>
       <c r="D898"/>
@@ -25787,7 +26011,7 @@
         <v>23</v>
       </c>
       <c r="B900" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C900"/>
       <c r="D900"/>
@@ -25815,7 +26039,7 @@
         <v>24</v>
       </c>
       <c r="B901" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C901"/>
       <c r="D901"/>
@@ -25843,7 +26067,7 @@
         <v>25</v>
       </c>
       <c r="B902" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C902"/>
       <c r="D902"/>
@@ -25897,7 +26121,7 @@
         <v>27</v>
       </c>
       <c r="B904" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C904"/>
       <c r="D904"/>
@@ -25925,7 +26149,7 @@
         <v>28</v>
       </c>
       <c r="B905" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C905"/>
       <c r="D905"/>
@@ -25953,7 +26177,7 @@
         <v>29</v>
       </c>
       <c r="B906" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C906"/>
       <c r="D906"/>
@@ -25981,7 +26205,7 @@
         <v>30</v>
       </c>
       <c r="B907" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C907"/>
       <c r="D907"/>
@@ -26009,7 +26233,7 @@
         <v>31</v>
       </c>
       <c r="B908" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C908"/>
       <c r="D908"/>
@@ -26037,7 +26261,7 @@
         <v>32</v>
       </c>
       <c r="B909" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C909"/>
       <c r="D909"/>
@@ -26065,7 +26289,7 @@
         <v>33</v>
       </c>
       <c r="B910" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C910"/>
       <c r="D910"/>
@@ -26093,7 +26317,7 @@
         <v>34</v>
       </c>
       <c r="B911" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C911"/>
       <c r="D911"/>
@@ -26121,7 +26345,7 @@
         <v>35</v>
       </c>
       <c r="B912" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C912"/>
       <c r="D912"/>
@@ -26177,7 +26401,7 @@
         <v>20</v>
       </c>
       <c r="B914" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C914"/>
       <c r="D914"/>
@@ -26205,7 +26429,7 @@
         <v>22</v>
       </c>
       <c r="B915" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C915"/>
       <c r="D915"/>
@@ -26233,7 +26457,7 @@
         <v>23</v>
       </c>
       <c r="B916" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C916"/>
       <c r="D916"/>
@@ -26261,7 +26485,7 @@
         <v>24</v>
       </c>
       <c r="B917" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C917"/>
       <c r="D917"/>
@@ -26289,7 +26513,7 @@
         <v>25</v>
       </c>
       <c r="B918" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C918"/>
       <c r="D918"/>
@@ -26317,7 +26541,7 @@
         <v>26</v>
       </c>
       <c r="B919" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C919"/>
       <c r="D919"/>
@@ -26345,7 +26569,7 @@
         <v>27</v>
       </c>
       <c r="B920" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C920"/>
       <c r="D920"/>
@@ -26373,7 +26597,7 @@
         <v>28</v>
       </c>
       <c r="B921" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C921"/>
       <c r="D921"/>
@@ -26401,7 +26625,7 @@
         <v>29</v>
       </c>
       <c r="B922" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C922"/>
       <c r="D922"/>
@@ -26429,7 +26653,7 @@
         <v>30</v>
       </c>
       <c r="B923" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C923"/>
       <c r="D923"/>
@@ -26457,7 +26681,7 @@
         <v>31</v>
       </c>
       <c r="B924" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C924"/>
       <c r="D924"/>
@@ -26485,7 +26709,7 @@
         <v>32</v>
       </c>
       <c r="B925" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C925"/>
       <c r="D925"/>
@@ -26513,7 +26737,7 @@
         <v>33</v>
       </c>
       <c r="B926" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C926"/>
       <c r="D926"/>
@@ -26541,7 +26765,7 @@
         <v>34</v>
       </c>
       <c r="B927" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C927"/>
       <c r="D927"/>
@@ -26569,7 +26793,7 @@
         <v>35</v>
       </c>
       <c r="B928" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C928"/>
       <c r="D928"/>
@@ -26597,7 +26821,7 @@
         <v>36</v>
       </c>
       <c r="B929" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C929"/>
       <c r="D929"/>
@@ -26625,7 +26849,7 @@
         <v>20</v>
       </c>
       <c r="B930" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C930"/>
       <c r="D930"/>
@@ -26679,7 +26903,7 @@
         <v>23</v>
       </c>
       <c r="B932" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C932"/>
       <c r="D932"/>
@@ -26707,7 +26931,7 @@
         <v>24</v>
       </c>
       <c r="B933" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C933"/>
       <c r="D933"/>
@@ -26735,7 +26959,7 @@
         <v>25</v>
       </c>
       <c r="B934" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C934"/>
       <c r="D934"/>
@@ -26789,7 +27013,7 @@
         <v>27</v>
       </c>
       <c r="B936" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C936"/>
       <c r="D936"/>
@@ -26817,7 +27041,7 @@
         <v>28</v>
       </c>
       <c r="B937" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C937"/>
       <c r="D937"/>
@@ -26845,7 +27069,7 @@
         <v>29</v>
       </c>
       <c r="B938" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C938"/>
       <c r="D938"/>
@@ -26873,7 +27097,7 @@
         <v>30</v>
       </c>
       <c r="B939" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C939"/>
       <c r="D939"/>
@@ -26901,7 +27125,7 @@
         <v>31</v>
       </c>
       <c r="B940" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C940"/>
       <c r="D940"/>
@@ -26929,7 +27153,7 @@
         <v>32</v>
       </c>
       <c r="B941" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C941"/>
       <c r="D941"/>
@@ -26957,7 +27181,7 @@
         <v>33</v>
       </c>
       <c r="B942" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C942"/>
       <c r="D942"/>
@@ -26985,7 +27209,7 @@
         <v>34</v>
       </c>
       <c r="B943" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C943"/>
       <c r="D943"/>
@@ -27013,7 +27237,7 @@
         <v>35</v>
       </c>
       <c r="B944" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C944"/>
       <c r="D944"/>
@@ -27069,7 +27293,7 @@
         <v>20</v>
       </c>
       <c r="B946" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C946"/>
       <c r="D946"/>
@@ -27097,7 +27321,7 @@
         <v>22</v>
       </c>
       <c r="B947" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C947"/>
       <c r="D947"/>
@@ -27125,7 +27349,7 @@
         <v>23</v>
       </c>
       <c r="B948" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C948"/>
       <c r="D948"/>
@@ -27153,7 +27377,7 @@
         <v>24</v>
       </c>
       <c r="B949" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C949"/>
       <c r="D949"/>
@@ -27181,7 +27405,7 @@
         <v>25</v>
       </c>
       <c r="B950" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C950"/>
       <c r="D950"/>
@@ -27209,7 +27433,7 @@
         <v>26</v>
       </c>
       <c r="B951" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C951"/>
       <c r="D951"/>
@@ -27237,7 +27461,7 @@
         <v>27</v>
       </c>
       <c r="B952" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C952"/>
       <c r="D952"/>
@@ -27265,7 +27489,7 @@
         <v>28</v>
       </c>
       <c r="B953" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C953"/>
       <c r="D953"/>
@@ -27293,7 +27517,7 @@
         <v>29</v>
       </c>
       <c r="B954" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C954"/>
       <c r="D954"/>
@@ -27321,7 +27545,7 @@
         <v>30</v>
       </c>
       <c r="B955" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C955"/>
       <c r="D955"/>
@@ -27349,7 +27573,7 @@
         <v>31</v>
       </c>
       <c r="B956" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C956"/>
       <c r="D956"/>
@@ -27377,7 +27601,7 @@
         <v>32</v>
       </c>
       <c r="B957" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C957"/>
       <c r="D957"/>
@@ -27405,7 +27629,7 @@
         <v>33</v>
       </c>
       <c r="B958" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C958"/>
       <c r="D958"/>
@@ -27433,7 +27657,7 @@
         <v>34</v>
       </c>
       <c r="B959" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C959"/>
       <c r="D959"/>
@@ -27461,7 +27685,7 @@
         <v>35</v>
       </c>
       <c r="B960" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C960"/>
       <c r="D960"/>
@@ -27489,7 +27713,7 @@
         <v>36</v>
       </c>
       <c r="B961" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C961"/>
       <c r="D961"/>
@@ -27538,7 +27762,9 @@
       <c r="Q962"/>
       <c r="R962"/>
       <c r="S962"/>
-      <c r="T962"/>
+      <c r="T962" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="963">
       <c r="A963" t="s">
@@ -27566,7 +27792,9 @@
       <c r="Q963"/>
       <c r="R963"/>
       <c r="S963"/>
-      <c r="T963"/>
+      <c r="T963" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="964">
       <c r="A964" t="s">
@@ -27594,7 +27822,9 @@
       <c r="Q964"/>
       <c r="R964"/>
       <c r="S964"/>
-      <c r="T964"/>
+      <c r="T964" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="965">
       <c r="A965" t="s">
@@ -27622,7 +27852,9 @@
       <c r="Q965"/>
       <c r="R965"/>
       <c r="S965"/>
-      <c r="T965"/>
+      <c r="T965" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="966">
       <c r="A966" t="s">
@@ -27650,7 +27882,9 @@
       <c r="Q966"/>
       <c r="R966"/>
       <c r="S966"/>
-      <c r="T966"/>
+      <c r="T966" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="967">
       <c r="A967" t="s">
@@ -27678,7 +27912,9 @@
       <c r="Q967"/>
       <c r="R967"/>
       <c r="S967"/>
-      <c r="T967"/>
+      <c r="T967" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="968">
       <c r="A968" t="s">
@@ -27706,7 +27942,9 @@
       <c r="Q968"/>
       <c r="R968"/>
       <c r="S968"/>
-      <c r="T968"/>
+      <c r="T968" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="969">
       <c r="A969" t="s">
@@ -27734,7 +27972,9 @@
       <c r="Q969"/>
       <c r="R969"/>
       <c r="S969"/>
-      <c r="T969"/>
+      <c r="T969" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="970">
       <c r="A970" t="s">
@@ -27762,7 +28002,9 @@
       <c r="Q970"/>
       <c r="R970"/>
       <c r="S970"/>
-      <c r="T970"/>
+      <c r="T970" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="971">
       <c r="A971" t="s">
@@ -27790,7 +28032,9 @@
       <c r="Q971"/>
       <c r="R971"/>
       <c r="S971"/>
-      <c r="T971"/>
+      <c r="T971" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="972">
       <c r="A972" t="s">
@@ -27818,7 +28062,9 @@
       <c r="Q972"/>
       <c r="R972"/>
       <c r="S972"/>
-      <c r="T972"/>
+      <c r="T972" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="973">
       <c r="A973" t="s">
@@ -27846,7 +28092,9 @@
       <c r="Q973"/>
       <c r="R973"/>
       <c r="S973"/>
-      <c r="T973"/>
+      <c r="T973" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="974">
       <c r="A974" t="s">
@@ -27874,7 +28122,9 @@
       <c r="Q974"/>
       <c r="R974"/>
       <c r="S974"/>
-      <c r="T974"/>
+      <c r="T974" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="975">
       <c r="A975" t="s">
@@ -27902,7 +28152,9 @@
       <c r="Q975"/>
       <c r="R975"/>
       <c r="S975"/>
-      <c r="T975"/>
+      <c r="T975" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="976">
       <c r="A976" t="s">
@@ -27930,7 +28182,9 @@
       <c r="Q976"/>
       <c r="R976"/>
       <c r="S976"/>
-      <c r="T976"/>
+      <c r="T976" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="977">
       <c r="A977" t="s">
@@ -27958,14 +28212,16 @@
       <c r="Q977"/>
       <c r="R977"/>
       <c r="S977"/>
-      <c r="T977"/>
+      <c r="T977" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="978">
       <c r="A978" t="s">
         <v>20</v>
       </c>
       <c r="B978" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C978"/>
       <c r="D978"/>
@@ -28021,7 +28277,7 @@
         <v>23</v>
       </c>
       <c r="B980" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C980"/>
       <c r="D980"/>
@@ -28049,7 +28305,7 @@
         <v>24</v>
       </c>
       <c r="B981" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C981"/>
       <c r="D981"/>
@@ -28077,7 +28333,7 @@
         <v>25</v>
       </c>
       <c r="B982" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C982"/>
       <c r="D982"/>
@@ -28133,7 +28389,7 @@
         <v>27</v>
       </c>
       <c r="B984" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C984"/>
       <c r="D984"/>
@@ -28161,7 +28417,7 @@
         <v>28</v>
       </c>
       <c r="B985" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C985"/>
       <c r="D985"/>
@@ -28189,7 +28445,7 @@
         <v>29</v>
       </c>
       <c r="B986" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C986"/>
       <c r="D986"/>
@@ -28217,7 +28473,7 @@
         <v>30</v>
       </c>
       <c r="B987" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C987"/>
       <c r="D987"/>
@@ -28245,7 +28501,7 @@
         <v>31</v>
       </c>
       <c r="B988" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C988"/>
       <c r="D988"/>
@@ -28273,7 +28529,7 @@
         <v>32</v>
       </c>
       <c r="B989" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C989"/>
       <c r="D989"/>
@@ -28301,7 +28557,7 @@
         <v>33</v>
       </c>
       <c r="B990" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C990"/>
       <c r="D990"/>
@@ -28329,7 +28585,7 @@
         <v>34</v>
       </c>
       <c r="B991" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C991"/>
       <c r="D991"/>
@@ -28357,7 +28613,7 @@
         <v>35</v>
       </c>
       <c r="B992" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C992"/>
       <c r="D992"/>
@@ -28413,7 +28669,7 @@
         <v>20</v>
       </c>
       <c r="B994" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C994"/>
       <c r="D994"/>
@@ -28441,7 +28697,7 @@
         <v>22</v>
       </c>
       <c r="B995" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C995"/>
       <c r="D995"/>
@@ -28469,7 +28725,7 @@
         <v>23</v>
       </c>
       <c r="B996" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C996"/>
       <c r="D996"/>
@@ -28497,7 +28753,7 @@
         <v>24</v>
       </c>
       <c r="B997" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C997"/>
       <c r="D997"/>
@@ -28525,7 +28781,7 @@
         <v>25</v>
       </c>
       <c r="B998" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C998"/>
       <c r="D998"/>
@@ -28553,7 +28809,7 @@
         <v>26</v>
       </c>
       <c r="B999" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C999"/>
       <c r="D999"/>
@@ -28581,7 +28837,7 @@
         <v>27</v>
       </c>
       <c r="B1000" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C1000"/>
       <c r="D1000"/>
@@ -28609,7 +28865,7 @@
         <v>28</v>
       </c>
       <c r="B1001" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C1001"/>
       <c r="D1001"/>
@@ -28637,7 +28893,7 @@
         <v>29</v>
       </c>
       <c r="B1002" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C1002"/>
       <c r="D1002"/>
@@ -28665,7 +28921,7 @@
         <v>30</v>
       </c>
       <c r="B1003" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C1003"/>
       <c r="D1003"/>
@@ -28693,7 +28949,7 @@
         <v>31</v>
       </c>
       <c r="B1004" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C1004"/>
       <c r="D1004"/>
@@ -28721,7 +28977,7 @@
         <v>32</v>
       </c>
       <c r="B1005" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C1005"/>
       <c r="D1005"/>
@@ -28749,7 +29005,7 @@
         <v>33</v>
       </c>
       <c r="B1006" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C1006"/>
       <c r="D1006"/>
@@ -28777,7 +29033,7 @@
         <v>34</v>
       </c>
       <c r="B1007" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C1007"/>
       <c r="D1007"/>
@@ -28805,7 +29061,7 @@
         <v>35</v>
       </c>
       <c r="B1008" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C1008"/>
       <c r="D1008"/>
@@ -28833,7 +29089,7 @@
         <v>36</v>
       </c>
       <c r="B1009" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C1009"/>
       <c r="D1009"/>
@@ -28861,7 +29117,7 @@
         <v>20</v>
       </c>
       <c r="B1010" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C1010"/>
       <c r="D1010"/>
@@ -28887,7 +29143,7 @@
         <v>22</v>
       </c>
       <c r="B1011" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C1011"/>
       <c r="D1011"/>
@@ -28915,7 +29171,7 @@
         <v>23</v>
       </c>
       <c r="B1012" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C1012"/>
       <c r="D1012"/>
@@ -28943,7 +29199,7 @@
         <v>24</v>
       </c>
       <c r="B1013" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C1013"/>
       <c r="D1013"/>
@@ -28969,7 +29225,7 @@
         <v>25</v>
       </c>
       <c r="B1014" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C1014"/>
       <c r="D1014"/>
@@ -28997,7 +29253,7 @@
         <v>26</v>
       </c>
       <c r="B1015" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C1015"/>
       <c r="D1015"/>
@@ -29023,7 +29279,7 @@
         <v>27</v>
       </c>
       <c r="B1016" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C1016"/>
       <c r="D1016"/>
@@ -29049,7 +29305,7 @@
         <v>28</v>
       </c>
       <c r="B1017" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C1017"/>
       <c r="D1017"/>
@@ -29077,7 +29333,7 @@
         <v>29</v>
       </c>
       <c r="B1018" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C1018"/>
       <c r="D1018"/>
@@ -29105,7 +29361,7 @@
         <v>30</v>
       </c>
       <c r="B1019" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C1019"/>
       <c r="D1019"/>
@@ -29133,7 +29389,7 @@
         <v>31</v>
       </c>
       <c r="B1020" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C1020"/>
       <c r="D1020"/>
@@ -29159,7 +29415,7 @@
         <v>32</v>
       </c>
       <c r="B1021" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C1021"/>
       <c r="D1021"/>
@@ -29185,7 +29441,7 @@
         <v>33</v>
       </c>
       <c r="B1022" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C1022"/>
       <c r="D1022"/>
@@ -29213,7 +29469,7 @@
         <v>34</v>
       </c>
       <c r="B1023" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C1023"/>
       <c r="D1023"/>
@@ -29239,7 +29495,7 @@
         <v>35</v>
       </c>
       <c r="B1024" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C1024"/>
       <c r="D1024"/>
@@ -29267,7 +29523,7 @@
         <v>36</v>
       </c>
       <c r="B1025" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C1025"/>
       <c r="D1025"/>
@@ -29293,7 +29549,7 @@
         <v>20</v>
       </c>
       <c r="B1026" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C1026"/>
       <c r="D1026"/>
@@ -29319,7 +29575,7 @@
         <v>22</v>
       </c>
       <c r="B1027" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C1027"/>
       <c r="D1027"/>
@@ -29347,7 +29603,7 @@
         <v>23</v>
       </c>
       <c r="B1028" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C1028"/>
       <c r="D1028"/>
@@ -29375,7 +29631,7 @@
         <v>24</v>
       </c>
       <c r="B1029" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C1029"/>
       <c r="D1029"/>
@@ -29401,7 +29657,7 @@
         <v>25</v>
       </c>
       <c r="B1030" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C1030"/>
       <c r="D1030"/>
@@ -29429,7 +29685,7 @@
         <v>26</v>
       </c>
       <c r="B1031" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C1031"/>
       <c r="D1031"/>
@@ -29455,7 +29711,7 @@
         <v>27</v>
       </c>
       <c r="B1032" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C1032"/>
       <c r="D1032"/>
@@ -29481,7 +29737,7 @@
         <v>28</v>
       </c>
       <c r="B1033" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C1033"/>
       <c r="D1033"/>
@@ -29509,7 +29765,7 @@
         <v>29</v>
       </c>
       <c r="B1034" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C1034"/>
       <c r="D1034"/>
@@ -29537,7 +29793,7 @@
         <v>30</v>
       </c>
       <c r="B1035" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C1035"/>
       <c r="D1035"/>
@@ -29565,7 +29821,7 @@
         <v>31</v>
       </c>
       <c r="B1036" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C1036"/>
       <c r="D1036"/>
@@ -29591,7 +29847,7 @@
         <v>32</v>
       </c>
       <c r="B1037" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C1037"/>
       <c r="D1037"/>
@@ -29617,7 +29873,7 @@
         <v>33</v>
       </c>
       <c r="B1038" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C1038"/>
       <c r="D1038"/>
@@ -29645,7 +29901,7 @@
         <v>34</v>
       </c>
       <c r="B1039" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C1039"/>
       <c r="D1039"/>
@@ -29671,7 +29927,7 @@
         <v>35</v>
       </c>
       <c r="B1040" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C1040"/>
       <c r="D1040"/>
@@ -29699,7 +29955,7 @@
         <v>36</v>
       </c>
       <c r="B1041" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C1041"/>
       <c r="D1041"/>
@@ -29725,7 +29981,7 @@
         <v>20</v>
       </c>
       <c r="B1042" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C1042"/>
       <c r="D1042"/>
@@ -29751,7 +30007,7 @@
         <v>22</v>
       </c>
       <c r="B1043" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C1043"/>
       <c r="D1043"/>
@@ -29779,7 +30035,7 @@
         <v>23</v>
       </c>
       <c r="B1044" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C1044"/>
       <c r="D1044"/>
@@ -29807,7 +30063,7 @@
         <v>24</v>
       </c>
       <c r="B1045" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C1045"/>
       <c r="D1045"/>
@@ -29833,7 +30089,7 @@
         <v>25</v>
       </c>
       <c r="B1046" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C1046"/>
       <c r="D1046"/>
@@ -29861,7 +30117,7 @@
         <v>26</v>
       </c>
       <c r="B1047" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C1047"/>
       <c r="D1047"/>
@@ -29887,7 +30143,7 @@
         <v>27</v>
       </c>
       <c r="B1048" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C1048"/>
       <c r="D1048"/>
@@ -29913,7 +30169,7 @@
         <v>28</v>
       </c>
       <c r="B1049" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C1049"/>
       <c r="D1049"/>
@@ -29941,7 +30197,7 @@
         <v>29</v>
       </c>
       <c r="B1050" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C1050"/>
       <c r="D1050"/>
@@ -29969,7 +30225,7 @@
         <v>30</v>
       </c>
       <c r="B1051" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C1051"/>
       <c r="D1051"/>
@@ -29997,7 +30253,7 @@
         <v>31</v>
       </c>
       <c r="B1052" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C1052"/>
       <c r="D1052"/>
@@ -30023,7 +30279,7 @@
         <v>32</v>
       </c>
       <c r="B1053" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C1053"/>
       <c r="D1053"/>
@@ -30049,7 +30305,7 @@
         <v>33</v>
       </c>
       <c r="B1054" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C1054"/>
       <c r="D1054"/>
@@ -30077,7 +30333,7 @@
         <v>34</v>
       </c>
       <c r="B1055" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C1055"/>
       <c r="D1055"/>
@@ -30103,7 +30359,7 @@
         <v>35</v>
       </c>
       <c r="B1056" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C1056"/>
       <c r="D1056"/>
@@ -30131,7 +30387,7 @@
         <v>36</v>
       </c>
       <c r="B1057" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C1057"/>
       <c r="D1057"/>
@@ -30589,7 +30845,7 @@
         <v>20</v>
       </c>
       <c r="B1074" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C1074"/>
       <c r="D1074"/>
@@ -30615,7 +30871,7 @@
         <v>22</v>
       </c>
       <c r="B1075" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C1075"/>
       <c r="D1075"/>
@@ -30643,7 +30899,7 @@
         <v>23</v>
       </c>
       <c r="B1076" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C1076"/>
       <c r="D1076"/>
@@ -30671,7 +30927,7 @@
         <v>24</v>
       </c>
       <c r="B1077" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C1077"/>
       <c r="D1077"/>
@@ -30697,7 +30953,7 @@
         <v>25</v>
       </c>
       <c r="B1078" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C1078"/>
       <c r="D1078"/>
@@ -30725,7 +30981,7 @@
         <v>26</v>
       </c>
       <c r="B1079" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C1079"/>
       <c r="D1079"/>
@@ -30751,7 +31007,7 @@
         <v>27</v>
       </c>
       <c r="B1080" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C1080"/>
       <c r="D1080"/>
@@ -30777,7 +31033,7 @@
         <v>28</v>
       </c>
       <c r="B1081" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C1081"/>
       <c r="D1081"/>
@@ -30805,7 +31061,7 @@
         <v>29</v>
       </c>
       <c r="B1082" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C1082"/>
       <c r="D1082"/>
@@ -30833,7 +31089,7 @@
         <v>30</v>
       </c>
       <c r="B1083" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C1083"/>
       <c r="D1083"/>
@@ -30861,7 +31117,7 @@
         <v>31</v>
       </c>
       <c r="B1084" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C1084"/>
       <c r="D1084"/>
@@ -30887,7 +31143,7 @@
         <v>32</v>
       </c>
       <c r="B1085" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C1085"/>
       <c r="D1085"/>
@@ -30913,7 +31169,7 @@
         <v>33</v>
       </c>
       <c r="B1086" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C1086"/>
       <c r="D1086"/>
@@ -30941,7 +31197,7 @@
         <v>34</v>
       </c>
       <c r="B1087" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C1087"/>
       <c r="D1087"/>
@@ -30967,7 +31223,7 @@
         <v>35</v>
       </c>
       <c r="B1088" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C1088"/>
       <c r="D1088"/>
@@ -30995,7 +31251,7 @@
         <v>36</v>
       </c>
       <c r="B1089" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C1089"/>
       <c r="D1089"/>
@@ -31021,7 +31277,7 @@
         <v>20</v>
       </c>
       <c r="B1090" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C1090"/>
       <c r="D1090"/>
@@ -31049,7 +31305,7 @@
         <v>22</v>
       </c>
       <c r="B1091" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C1091"/>
       <c r="D1091"/>
@@ -31075,7 +31331,7 @@
         <v>23</v>
       </c>
       <c r="B1092" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C1092"/>
       <c r="D1092"/>
@@ -31101,7 +31357,7 @@
         <v>24</v>
       </c>
       <c r="B1093" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C1093"/>
       <c r="D1093"/>
@@ -31129,7 +31385,7 @@
         <v>25</v>
       </c>
       <c r="B1094" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C1094"/>
       <c r="D1094"/>
@@ -31155,7 +31411,7 @@
         <v>26</v>
       </c>
       <c r="B1095" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C1095"/>
       <c r="D1095"/>
@@ -31183,7 +31439,7 @@
         <v>27</v>
       </c>
       <c r="B1096" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C1096"/>
       <c r="D1096"/>
@@ -31211,7 +31467,7 @@
         <v>28</v>
       </c>
       <c r="B1097" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C1097"/>
       <c r="D1097"/>
@@ -31237,7 +31493,7 @@
         <v>29</v>
       </c>
       <c r="B1098" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C1098"/>
       <c r="D1098"/>
@@ -31263,7 +31519,7 @@
         <v>30</v>
       </c>
       <c r="B1099" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C1099"/>
       <c r="D1099"/>
@@ -31289,7 +31545,7 @@
         <v>31</v>
       </c>
       <c r="B1100" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C1100"/>
       <c r="D1100"/>
@@ -31317,7 +31573,7 @@
         <v>32</v>
       </c>
       <c r="B1101" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C1101"/>
       <c r="D1101"/>
@@ -31345,7 +31601,7 @@
         <v>33</v>
       </c>
       <c r="B1102" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C1102"/>
       <c r="D1102"/>
@@ -31371,7 +31627,7 @@
         <v>34</v>
       </c>
       <c r="B1103" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C1103"/>
       <c r="D1103"/>
@@ -31399,7 +31655,7 @@
         <v>35</v>
       </c>
       <c r="B1104" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C1104"/>
       <c r="D1104"/>
@@ -31425,7 +31681,7 @@
         <v>36</v>
       </c>
       <c r="B1105" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C1105"/>
       <c r="D1105"/>
@@ -31453,7 +31709,7 @@
         <v>20</v>
       </c>
       <c r="B1106" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C1106"/>
       <c r="D1106"/>
@@ -31481,7 +31737,7 @@
         <v>22</v>
       </c>
       <c r="B1107" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C1107"/>
       <c r="D1107"/>
@@ -31507,7 +31763,7 @@
         <v>23</v>
       </c>
       <c r="B1108" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C1108"/>
       <c r="D1108"/>
@@ -31533,7 +31789,7 @@
         <v>24</v>
       </c>
       <c r="B1109" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C1109"/>
       <c r="D1109"/>
@@ -31561,7 +31817,7 @@
         <v>25</v>
       </c>
       <c r="B1110" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C1110"/>
       <c r="D1110"/>
@@ -31587,7 +31843,7 @@
         <v>26</v>
       </c>
       <c r="B1111" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C1111"/>
       <c r="D1111"/>
@@ -31615,7 +31871,7 @@
         <v>27</v>
       </c>
       <c r="B1112" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C1112"/>
       <c r="D1112"/>
@@ -31643,7 +31899,7 @@
         <v>28</v>
       </c>
       <c r="B1113" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C1113"/>
       <c r="D1113"/>
@@ -31669,7 +31925,7 @@
         <v>29</v>
       </c>
       <c r="B1114" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C1114"/>
       <c r="D1114"/>
@@ -31695,7 +31951,7 @@
         <v>30</v>
       </c>
       <c r="B1115" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C1115"/>
       <c r="D1115"/>
@@ -31721,7 +31977,7 @@
         <v>31</v>
       </c>
       <c r="B1116" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C1116"/>
       <c r="D1116"/>
@@ -31749,7 +32005,7 @@
         <v>32</v>
       </c>
       <c r="B1117" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C1117"/>
       <c r="D1117"/>
@@ -31777,7 +32033,7 @@
         <v>33</v>
       </c>
       <c r="B1118" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C1118"/>
       <c r="D1118"/>
@@ -31803,7 +32059,7 @@
         <v>34</v>
       </c>
       <c r="B1119" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C1119"/>
       <c r="D1119"/>
@@ -31831,7 +32087,7 @@
         <v>35</v>
       </c>
       <c r="B1120" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C1120"/>
       <c r="D1120"/>
@@ -31857,7 +32113,7 @@
         <v>36</v>
       </c>
       <c r="B1121" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C1121"/>
       <c r="D1121"/>
@@ -31885,7 +32141,7 @@
         <v>20</v>
       </c>
       <c r="B1122" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C1122"/>
       <c r="D1122"/>
@@ -31913,7 +32169,7 @@
         <v>22</v>
       </c>
       <c r="B1123" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C1123"/>
       <c r="D1123"/>
@@ -31939,7 +32195,7 @@
         <v>23</v>
       </c>
       <c r="B1124" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C1124"/>
       <c r="D1124"/>
@@ -31965,7 +32221,7 @@
         <v>24</v>
       </c>
       <c r="B1125" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C1125"/>
       <c r="D1125"/>
@@ -31993,7 +32249,7 @@
         <v>25</v>
       </c>
       <c r="B1126" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C1126"/>
       <c r="D1126"/>
@@ -32019,7 +32275,7 @@
         <v>26</v>
       </c>
       <c r="B1127" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C1127"/>
       <c r="D1127"/>
@@ -32047,7 +32303,7 @@
         <v>27</v>
       </c>
       <c r="B1128" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C1128"/>
       <c r="D1128"/>
@@ -32075,7 +32331,7 @@
         <v>28</v>
       </c>
       <c r="B1129" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C1129"/>
       <c r="D1129"/>
@@ -32101,7 +32357,7 @@
         <v>29</v>
       </c>
       <c r="B1130" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C1130"/>
       <c r="D1130"/>
@@ -32127,7 +32383,7 @@
         <v>30</v>
       </c>
       <c r="B1131" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C1131"/>
       <c r="D1131"/>
@@ -32153,7 +32409,7 @@
         <v>31</v>
       </c>
       <c r="B1132" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C1132"/>
       <c r="D1132"/>
@@ -32181,7 +32437,7 @@
         <v>32</v>
       </c>
       <c r="B1133" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C1133"/>
       <c r="D1133"/>
@@ -32209,7 +32465,7 @@
         <v>33</v>
       </c>
       <c r="B1134" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C1134"/>
       <c r="D1134"/>
@@ -32235,7 +32491,7 @@
         <v>34</v>
       </c>
       <c r="B1135" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C1135"/>
       <c r="D1135"/>
@@ -32263,7 +32519,7 @@
         <v>35</v>
       </c>
       <c r="B1136" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C1136"/>
       <c r="D1136"/>
@@ -32289,7 +32545,7 @@
         <v>36</v>
       </c>
       <c r="B1137" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C1137"/>
       <c r="D1137"/>
@@ -32749,7 +33005,7 @@
         <v>20</v>
       </c>
       <c r="B1154" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C1154"/>
       <c r="D1154"/>
@@ -32777,7 +33033,7 @@
         <v>22</v>
       </c>
       <c r="B1155" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C1155"/>
       <c r="D1155"/>
@@ -32803,7 +33059,7 @@
         <v>23</v>
       </c>
       <c r="B1156" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C1156"/>
       <c r="D1156"/>
@@ -32829,7 +33085,7 @@
         <v>24</v>
       </c>
       <c r="B1157" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C1157"/>
       <c r="D1157"/>
@@ -32857,7 +33113,7 @@
         <v>25</v>
       </c>
       <c r="B1158" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C1158"/>
       <c r="D1158"/>
@@ -32883,7 +33139,7 @@
         <v>26</v>
       </c>
       <c r="B1159" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C1159"/>
       <c r="D1159"/>
@@ -32911,7 +33167,7 @@
         <v>27</v>
       </c>
       <c r="B1160" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C1160"/>
       <c r="D1160"/>
@@ -32939,7 +33195,7 @@
         <v>28</v>
       </c>
       <c r="B1161" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C1161"/>
       <c r="D1161"/>
@@ -32965,7 +33221,7 @@
         <v>29</v>
       </c>
       <c r="B1162" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C1162"/>
       <c r="D1162"/>
@@ -32991,7 +33247,7 @@
         <v>30</v>
       </c>
       <c r="B1163" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C1163"/>
       <c r="D1163"/>
@@ -33017,7 +33273,7 @@
         <v>31</v>
       </c>
       <c r="B1164" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C1164"/>
       <c r="D1164"/>
@@ -33045,7 +33301,7 @@
         <v>32</v>
       </c>
       <c r="B1165" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C1165"/>
       <c r="D1165"/>
@@ -33073,7 +33329,7 @@
         <v>33</v>
       </c>
       <c r="B1166" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C1166"/>
       <c r="D1166"/>
@@ -33099,7 +33355,7 @@
         <v>34</v>
       </c>
       <c r="B1167" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C1167"/>
       <c r="D1167"/>
@@ -33127,7 +33383,7 @@
         <v>35</v>
       </c>
       <c r="B1168" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C1168"/>
       <c r="D1168"/>
@@ -33153,7 +33409,7 @@
         <v>36</v>
       </c>
       <c r="B1169" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C1169"/>
       <c r="D1169"/>
@@ -33181,7 +33437,7 @@
         <v>20</v>
       </c>
       <c r="B1170" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C1170"/>
       <c r="D1170"/>
@@ -33209,7 +33465,7 @@
         <v>22</v>
       </c>
       <c r="B1171" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C1171"/>
       <c r="D1171"/>
@@ -33235,7 +33491,7 @@
         <v>23</v>
       </c>
       <c r="B1172" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C1172"/>
       <c r="D1172"/>
@@ -33261,7 +33517,7 @@
         <v>24</v>
       </c>
       <c r="B1173" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C1173"/>
       <c r="D1173"/>
@@ -33289,7 +33545,7 @@
         <v>25</v>
       </c>
       <c r="B1174" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C1174"/>
       <c r="D1174"/>
@@ -33315,7 +33571,7 @@
         <v>26</v>
       </c>
       <c r="B1175" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C1175"/>
       <c r="D1175"/>
@@ -33343,7 +33599,7 @@
         <v>27</v>
       </c>
       <c r="B1176" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C1176"/>
       <c r="D1176"/>
@@ -33371,7 +33627,7 @@
         <v>28</v>
       </c>
       <c r="B1177" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C1177"/>
       <c r="D1177"/>
@@ -33397,7 +33653,7 @@
         <v>29</v>
       </c>
       <c r="B1178" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C1178"/>
       <c r="D1178"/>
@@ -33423,7 +33679,7 @@
         <v>30</v>
       </c>
       <c r="B1179" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C1179"/>
       <c r="D1179"/>
@@ -33449,7 +33705,7 @@
         <v>31</v>
       </c>
       <c r="B1180" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C1180"/>
       <c r="D1180"/>
@@ -33477,7 +33733,7 @@
         <v>32</v>
       </c>
       <c r="B1181" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C1181"/>
       <c r="D1181"/>
@@ -33505,7 +33761,7 @@
         <v>33</v>
       </c>
       <c r="B1182" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C1182"/>
       <c r="D1182"/>
@@ -33531,7 +33787,7 @@
         <v>34</v>
       </c>
       <c r="B1183" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C1183"/>
       <c r="D1183"/>
@@ -33559,7 +33815,7 @@
         <v>35</v>
       </c>
       <c r="B1184" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C1184"/>
       <c r="D1184"/>
@@ -33585,7 +33841,7 @@
         <v>36</v>
       </c>
       <c r="B1185" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C1185"/>
       <c r="D1185"/>
@@ -34037,7 +34293,7 @@
         <v>20</v>
       </c>
       <c r="B1202" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C1202"/>
       <c r="D1202"/>
@@ -34065,7 +34321,7 @@
         <v>22</v>
       </c>
       <c r="B1203" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C1203"/>
       <c r="D1203"/>
@@ -34093,7 +34349,7 @@
         <v>23</v>
       </c>
       <c r="B1204" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C1204"/>
       <c r="D1204"/>
@@ -34121,7 +34377,7 @@
         <v>24</v>
       </c>
       <c r="B1205" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C1205"/>
       <c r="D1205"/>
@@ -34149,7 +34405,7 @@
         <v>25</v>
       </c>
       <c r="B1206" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C1206"/>
       <c r="D1206"/>
@@ -34177,7 +34433,7 @@
         <v>26</v>
       </c>
       <c r="B1207" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C1207"/>
       <c r="D1207"/>
@@ -34205,7 +34461,7 @@
         <v>27</v>
       </c>
       <c r="B1208" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C1208"/>
       <c r="D1208"/>
@@ -34233,7 +34489,7 @@
         <v>28</v>
       </c>
       <c r="B1209" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C1209"/>
       <c r="D1209"/>
@@ -34261,7 +34517,7 @@
         <v>29</v>
       </c>
       <c r="B1210" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C1210"/>
       <c r="D1210"/>
@@ -34289,7 +34545,7 @@
         <v>30</v>
       </c>
       <c r="B1211" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C1211"/>
       <c r="D1211"/>
@@ -34317,7 +34573,7 @@
         <v>31</v>
       </c>
       <c r="B1212" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C1212"/>
       <c r="D1212"/>
@@ -34345,7 +34601,7 @@
         <v>32</v>
       </c>
       <c r="B1213" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C1213"/>
       <c r="D1213"/>
@@ -34373,7 +34629,7 @@
         <v>33</v>
       </c>
       <c r="B1214" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C1214"/>
       <c r="D1214"/>
@@ -34401,7 +34657,7 @@
         <v>34</v>
       </c>
       <c r="B1215" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C1215"/>
       <c r="D1215"/>
@@ -34429,7 +34685,7 @@
         <v>35</v>
       </c>
       <c r="B1216" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C1216"/>
       <c r="D1216"/>
@@ -34457,7 +34713,7 @@
         <v>36</v>
       </c>
       <c r="B1217" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C1217"/>
       <c r="D1217"/>
@@ -34485,7 +34741,7 @@
         <v>20</v>
       </c>
       <c r="B1218" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C1218"/>
       <c r="D1218"/>
@@ -34513,7 +34769,7 @@
         <v>22</v>
       </c>
       <c r="B1219" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C1219"/>
       <c r="D1219"/>
@@ -34541,7 +34797,7 @@
         <v>23</v>
       </c>
       <c r="B1220" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C1220"/>
       <c r="D1220"/>
@@ -34569,7 +34825,7 @@
         <v>24</v>
       </c>
       <c r="B1221" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C1221"/>
       <c r="D1221"/>
@@ -34597,7 +34853,7 @@
         <v>25</v>
       </c>
       <c r="B1222" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C1222"/>
       <c r="D1222"/>
@@ -34625,7 +34881,7 @@
         <v>26</v>
       </c>
       <c r="B1223" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C1223"/>
       <c r="D1223"/>
@@ -34653,7 +34909,7 @@
         <v>27</v>
       </c>
       <c r="B1224" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C1224"/>
       <c r="D1224"/>
@@ -34681,7 +34937,7 @@
         <v>28</v>
       </c>
       <c r="B1225" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C1225"/>
       <c r="D1225"/>
@@ -34709,7 +34965,7 @@
         <v>29</v>
       </c>
       <c r="B1226" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C1226"/>
       <c r="D1226"/>
@@ -34737,7 +34993,7 @@
         <v>30</v>
       </c>
       <c r="B1227" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C1227"/>
       <c r="D1227"/>
@@ -34765,7 +35021,7 @@
         <v>31</v>
       </c>
       <c r="B1228" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C1228"/>
       <c r="D1228"/>
@@ -34793,7 +35049,7 @@
         <v>32</v>
       </c>
       <c r="B1229" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C1229"/>
       <c r="D1229"/>
@@ -34821,7 +35077,7 @@
         <v>33</v>
       </c>
       <c r="B1230" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C1230"/>
       <c r="D1230"/>
@@ -34849,7 +35105,7 @@
         <v>34</v>
       </c>
       <c r="B1231" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C1231"/>
       <c r="D1231"/>
@@ -34877,7 +35133,7 @@
         <v>35</v>
       </c>
       <c r="B1232" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C1232"/>
       <c r="D1232"/>
@@ -34905,7 +35161,7 @@
         <v>36</v>
       </c>
       <c r="B1233" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C1233"/>
       <c r="D1233"/>
@@ -34933,7 +35189,7 @@
         <v>20</v>
       </c>
       <c r="B1234" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C1234"/>
       <c r="D1234"/>
@@ -34961,7 +35217,7 @@
         <v>22</v>
       </c>
       <c r="B1235" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C1235"/>
       <c r="D1235"/>
@@ -34989,7 +35245,7 @@
         <v>23</v>
       </c>
       <c r="B1236" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C1236"/>
       <c r="D1236"/>
@@ -35017,7 +35273,7 @@
         <v>24</v>
       </c>
       <c r="B1237" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C1237"/>
       <c r="D1237"/>
@@ -35045,7 +35301,7 @@
         <v>25</v>
       </c>
       <c r="B1238" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C1238"/>
       <c r="D1238"/>
@@ -35073,7 +35329,7 @@
         <v>26</v>
       </c>
       <c r="B1239" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C1239"/>
       <c r="D1239"/>
@@ -35101,7 +35357,7 @@
         <v>27</v>
       </c>
       <c r="B1240" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C1240"/>
       <c r="D1240"/>
@@ -35129,7 +35385,7 @@
         <v>28</v>
       </c>
       <c r="B1241" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C1241"/>
       <c r="D1241"/>
@@ -35157,7 +35413,7 @@
         <v>29</v>
       </c>
       <c r="B1242" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C1242"/>
       <c r="D1242"/>
@@ -35185,7 +35441,7 @@
         <v>30</v>
       </c>
       <c r="B1243" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C1243"/>
       <c r="D1243"/>
@@ -35213,7 +35469,7 @@
         <v>31</v>
       </c>
       <c r="B1244" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C1244"/>
       <c r="D1244"/>
@@ -35241,7 +35497,7 @@
         <v>32</v>
       </c>
       <c r="B1245" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C1245"/>
       <c r="D1245"/>
@@ -35269,7 +35525,7 @@
         <v>33</v>
       </c>
       <c r="B1246" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C1246"/>
       <c r="D1246"/>
@@ -35297,7 +35553,7 @@
         <v>34</v>
       </c>
       <c r="B1247" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C1247"/>
       <c r="D1247"/>
@@ -35325,7 +35581,7 @@
         <v>35</v>
       </c>
       <c r="B1248" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C1248"/>
       <c r="D1248"/>
@@ -35353,7 +35609,7 @@
         <v>36</v>
       </c>
       <c r="B1249" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C1249"/>
       <c r="D1249"/>
@@ -35381,7 +35637,7 @@
         <v>20</v>
       </c>
       <c r="B1250" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C1250"/>
       <c r="D1250"/>
@@ -35409,7 +35665,7 @@
         <v>22</v>
       </c>
       <c r="B1251" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C1251"/>
       <c r="D1251"/>
@@ -35437,7 +35693,7 @@
         <v>23</v>
       </c>
       <c r="B1252" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C1252"/>
       <c r="D1252"/>
@@ -35465,7 +35721,7 @@
         <v>24</v>
       </c>
       <c r="B1253" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C1253"/>
       <c r="D1253"/>
@@ -35493,7 +35749,7 @@
         <v>25</v>
       </c>
       <c r="B1254" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C1254"/>
       <c r="D1254"/>
@@ -35521,7 +35777,7 @@
         <v>26</v>
       </c>
       <c r="B1255" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C1255"/>
       <c r="D1255"/>
@@ -35549,7 +35805,7 @@
         <v>27</v>
       </c>
       <c r="B1256" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C1256"/>
       <c r="D1256"/>
@@ -35577,7 +35833,7 @@
         <v>28</v>
       </c>
       <c r="B1257" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C1257"/>
       <c r="D1257"/>
@@ -35605,7 +35861,7 @@
         <v>29</v>
       </c>
       <c r="B1258" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C1258"/>
       <c r="D1258"/>
@@ -35633,7 +35889,7 @@
         <v>30</v>
       </c>
       <c r="B1259" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C1259"/>
       <c r="D1259"/>
@@ -35661,7 +35917,7 @@
         <v>31</v>
       </c>
       <c r="B1260" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C1260"/>
       <c r="D1260"/>
@@ -35689,7 +35945,7 @@
         <v>32</v>
       </c>
       <c r="B1261" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C1261"/>
       <c r="D1261"/>
@@ -35717,7 +35973,7 @@
         <v>33</v>
       </c>
       <c r="B1262" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C1262"/>
       <c r="D1262"/>
@@ -35745,7 +36001,7 @@
         <v>34</v>
       </c>
       <c r="B1263" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C1263"/>
       <c r="D1263"/>
@@ -35773,7 +36029,7 @@
         <v>35</v>
       </c>
       <c r="B1264" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C1264"/>
       <c r="D1264"/>
@@ -35801,7 +36057,7 @@
         <v>36</v>
       </c>
       <c r="B1265" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C1265"/>
       <c r="D1265"/>
@@ -36277,7 +36533,7 @@
         <v>20</v>
       </c>
       <c r="B1282" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C1282"/>
       <c r="D1282"/>
@@ -36305,7 +36561,7 @@
         <v>22</v>
       </c>
       <c r="B1283" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C1283"/>
       <c r="D1283"/>
@@ -36333,7 +36589,7 @@
         <v>23</v>
       </c>
       <c r="B1284" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C1284"/>
       <c r="D1284"/>
@@ -36361,7 +36617,7 @@
         <v>24</v>
       </c>
       <c r="B1285" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C1285"/>
       <c r="D1285"/>
@@ -36389,7 +36645,7 @@
         <v>25</v>
       </c>
       <c r="B1286" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C1286"/>
       <c r="D1286"/>
@@ -36417,7 +36673,7 @@
         <v>26</v>
       </c>
       <c r="B1287" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C1287"/>
       <c r="D1287"/>
@@ -36445,7 +36701,7 @@
         <v>27</v>
       </c>
       <c r="B1288" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C1288"/>
       <c r="D1288"/>
@@ -36473,7 +36729,7 @@
         <v>28</v>
       </c>
       <c r="B1289" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C1289"/>
       <c r="D1289"/>
@@ -36501,7 +36757,7 @@
         <v>29</v>
       </c>
       <c r="B1290" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C1290"/>
       <c r="D1290"/>
@@ -36529,7 +36785,7 @@
         <v>30</v>
       </c>
       <c r="B1291" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C1291"/>
       <c r="D1291"/>
@@ -36557,7 +36813,7 @@
         <v>31</v>
       </c>
       <c r="B1292" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C1292"/>
       <c r="D1292"/>
@@ -36585,7 +36841,7 @@
         <v>32</v>
       </c>
       <c r="B1293" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C1293"/>
       <c r="D1293"/>
@@ -36613,7 +36869,7 @@
         <v>33</v>
       </c>
       <c r="B1294" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C1294"/>
       <c r="D1294"/>
@@ -36641,7 +36897,7 @@
         <v>34</v>
       </c>
       <c r="B1295" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C1295"/>
       <c r="D1295"/>
@@ -36669,7 +36925,7 @@
         <v>35</v>
       </c>
       <c r="B1296" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C1296"/>
       <c r="D1296"/>
@@ -36697,7 +36953,7 @@
         <v>36</v>
       </c>
       <c r="B1297" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C1297"/>
       <c r="D1297"/>
@@ -38069,7 +38325,7 @@
         <v>20</v>
       </c>
       <c r="B1346" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C1346"/>
       <c r="D1346"/>
@@ -38097,7 +38353,7 @@
         <v>22</v>
       </c>
       <c r="B1347" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C1347"/>
       <c r="D1347"/>
@@ -38125,7 +38381,7 @@
         <v>23</v>
       </c>
       <c r="B1348" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C1348"/>
       <c r="D1348"/>
@@ -38153,7 +38409,7 @@
         <v>24</v>
       </c>
       <c r="B1349" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C1349"/>
       <c r="D1349"/>
@@ -38181,7 +38437,7 @@
         <v>25</v>
       </c>
       <c r="B1350" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C1350"/>
       <c r="D1350"/>
@@ -38209,7 +38465,7 @@
         <v>26</v>
       </c>
       <c r="B1351" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C1351"/>
       <c r="D1351"/>
@@ -38237,7 +38493,7 @@
         <v>27</v>
       </c>
       <c r="B1352" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C1352"/>
       <c r="D1352"/>
@@ -38265,7 +38521,7 @@
         <v>28</v>
       </c>
       <c r="B1353" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C1353"/>
       <c r="D1353"/>
@@ -38293,7 +38549,7 @@
         <v>29</v>
       </c>
       <c r="B1354" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C1354"/>
       <c r="D1354"/>
@@ -38321,7 +38577,7 @@
         <v>30</v>
       </c>
       <c r="B1355" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C1355"/>
       <c r="D1355"/>
@@ -38349,7 +38605,7 @@
         <v>31</v>
       </c>
       <c r="B1356" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C1356"/>
       <c r="D1356"/>
@@ -38377,7 +38633,7 @@
         <v>32</v>
       </c>
       <c r="B1357" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C1357"/>
       <c r="D1357"/>
@@ -38405,7 +38661,7 @@
         <v>33</v>
       </c>
       <c r="B1358" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C1358"/>
       <c r="D1358"/>
@@ -38433,7 +38689,7 @@
         <v>34</v>
       </c>
       <c r="B1359" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C1359"/>
       <c r="D1359"/>
@@ -38461,7 +38717,7 @@
         <v>35</v>
       </c>
       <c r="B1360" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C1360"/>
       <c r="D1360"/>
@@ -38489,7 +38745,7 @@
         <v>36</v>
       </c>
       <c r="B1361" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C1361"/>
       <c r="D1361"/>
@@ -38517,7 +38773,7 @@
         <v>20</v>
       </c>
       <c r="B1362" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C1362"/>
       <c r="D1362"/>
@@ -38545,7 +38801,7 @@
         <v>22</v>
       </c>
       <c r="B1363" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C1363"/>
       <c r="D1363"/>
@@ -38573,7 +38829,7 @@
         <v>23</v>
       </c>
       <c r="B1364" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C1364"/>
       <c r="D1364"/>
@@ -38601,7 +38857,7 @@
         <v>24</v>
       </c>
       <c r="B1365" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C1365"/>
       <c r="D1365"/>
@@ -38629,7 +38885,7 @@
         <v>25</v>
       </c>
       <c r="B1366" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C1366"/>
       <c r="D1366"/>
@@ -38657,7 +38913,7 @@
         <v>26</v>
       </c>
       <c r="B1367" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C1367"/>
       <c r="D1367"/>
@@ -38685,7 +38941,7 @@
         <v>27</v>
       </c>
       <c r="B1368" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C1368"/>
       <c r="D1368"/>
@@ -38713,7 +38969,7 @@
         <v>28</v>
       </c>
       <c r="B1369" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C1369"/>
       <c r="D1369"/>
@@ -38741,7 +38997,7 @@
         <v>29</v>
       </c>
       <c r="B1370" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C1370"/>
       <c r="D1370"/>
@@ -38769,7 +39025,7 @@
         <v>30</v>
       </c>
       <c r="B1371" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C1371"/>
       <c r="D1371"/>
@@ -38797,7 +39053,7 @@
         <v>31</v>
       </c>
       <c r="B1372" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C1372"/>
       <c r="D1372"/>
@@ -38825,7 +39081,7 @@
         <v>32</v>
       </c>
       <c r="B1373" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C1373"/>
       <c r="D1373"/>
@@ -38853,7 +39109,7 @@
         <v>33</v>
       </c>
       <c r="B1374" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C1374"/>
       <c r="D1374"/>
@@ -38881,7 +39137,7 @@
         <v>34</v>
       </c>
       <c r="B1375" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C1375"/>
       <c r="D1375"/>
@@ -38909,7 +39165,7 @@
         <v>35</v>
       </c>
       <c r="B1376" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C1376"/>
       <c r="D1376"/>
@@ -38937,7 +39193,7 @@
         <v>36</v>
       </c>
       <c r="B1377" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C1377"/>
       <c r="D1377"/>
@@ -39413,7 +39669,7 @@
         <v>20</v>
       </c>
       <c r="B1394" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C1394"/>
       <c r="D1394"/>
@@ -39441,7 +39697,7 @@
         <v>22</v>
       </c>
       <c r="B1395" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C1395"/>
       <c r="D1395"/>
@@ -39469,7 +39725,7 @@
         <v>23</v>
       </c>
       <c r="B1396" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C1396"/>
       <c r="D1396"/>
@@ -39497,7 +39753,7 @@
         <v>24</v>
       </c>
       <c r="B1397" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C1397"/>
       <c r="D1397"/>
@@ -39525,7 +39781,7 @@
         <v>25</v>
       </c>
       <c r="B1398" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C1398"/>
       <c r="D1398"/>
@@ -39553,7 +39809,7 @@
         <v>26</v>
       </c>
       <c r="B1399" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C1399"/>
       <c r="D1399"/>
@@ -39581,7 +39837,7 @@
         <v>27</v>
       </c>
       <c r="B1400" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C1400"/>
       <c r="D1400"/>
@@ -39609,7 +39865,7 @@
         <v>28</v>
       </c>
       <c r="B1401" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C1401"/>
       <c r="D1401"/>
@@ -39637,7 +39893,7 @@
         <v>29</v>
       </c>
       <c r="B1402" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C1402"/>
       <c r="D1402"/>
@@ -39665,7 +39921,7 @@
         <v>30</v>
       </c>
       <c r="B1403" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C1403"/>
       <c r="D1403"/>
@@ -39693,7 +39949,7 @@
         <v>31</v>
       </c>
       <c r="B1404" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C1404"/>
       <c r="D1404"/>
@@ -39721,7 +39977,7 @@
         <v>32</v>
       </c>
       <c r="B1405" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C1405"/>
       <c r="D1405"/>
@@ -39749,7 +40005,7 @@
         <v>33</v>
       </c>
       <c r="B1406" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C1406"/>
       <c r="D1406"/>
@@ -39777,7 +40033,7 @@
         <v>34</v>
       </c>
       <c r="B1407" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C1407"/>
       <c r="D1407"/>
@@ -39805,7 +40061,7 @@
         <v>35</v>
       </c>
       <c r="B1408" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C1408"/>
       <c r="D1408"/>
@@ -39833,7 +40089,7 @@
         <v>36</v>
       </c>
       <c r="B1409" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C1409"/>
       <c r="D1409"/>
@@ -40309,7 +40565,7 @@
         <v>20</v>
       </c>
       <c r="B1426" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C1426"/>
       <c r="D1426"/>
@@ -40337,7 +40593,7 @@
         <v>20</v>
       </c>
       <c r="B1427" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C1427"/>
       <c r="D1427"/>
@@ -40365,7 +40621,7 @@
         <v>20</v>
       </c>
       <c r="B1428" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C1428"/>
       <c r="D1428"/>
@@ -40393,7 +40649,7 @@
         <v>20</v>
       </c>
       <c r="B1429" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C1429"/>
       <c r="D1429"/>
@@ -40421,7 +40677,7 @@
         <v>20</v>
       </c>
       <c r="B1430" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C1430"/>
       <c r="D1430"/>
@@ -40449,7 +40705,7 @@
         <v>20</v>
       </c>
       <c r="B1431" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C1431"/>
       <c r="D1431"/>
@@ -40477,7 +40733,7 @@
         <v>23</v>
       </c>
       <c r="B1432" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C1432"/>
       <c r="D1432"/>
@@ -40505,7 +40761,7 @@
         <v>23</v>
       </c>
       <c r="B1433" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C1433"/>
       <c r="D1433"/>
@@ -40533,7 +40789,7 @@
         <v>23</v>
       </c>
       <c r="B1434" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C1434"/>
       <c r="D1434"/>
@@ -40561,7 +40817,7 @@
         <v>23</v>
       </c>
       <c r="B1435" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C1435"/>
       <c r="D1435"/>
@@ -40589,7 +40845,7 @@
         <v>23</v>
       </c>
       <c r="B1436" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C1436"/>
       <c r="D1436"/>
@@ -40617,7 +40873,7 @@
         <v>23</v>
       </c>
       <c r="B1437" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C1437"/>
       <c r="D1437"/>
@@ -40645,7 +40901,7 @@
         <v>24</v>
       </c>
       <c r="B1438" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C1438"/>
       <c r="D1438"/>
@@ -40673,7 +40929,7 @@
         <v>24</v>
       </c>
       <c r="B1439" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C1439"/>
       <c r="D1439"/>
@@ -40701,7 +40957,7 @@
         <v>24</v>
       </c>
       <c r="B1440" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C1440"/>
       <c r="D1440"/>
@@ -40729,7 +40985,7 @@
         <v>24</v>
       </c>
       <c r="B1441" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C1441"/>
       <c r="D1441"/>
@@ -40785,7 +41041,7 @@
         <v>24</v>
       </c>
       <c r="B1443" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C1443"/>
       <c r="D1443"/>
@@ -40813,7 +41069,7 @@
         <v>25</v>
       </c>
       <c r="B1444" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C1444"/>
       <c r="D1444"/>
@@ -40841,7 +41097,7 @@
         <v>25</v>
       </c>
       <c r="B1445" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C1445"/>
       <c r="D1445"/>
@@ -40869,7 +41125,7 @@
         <v>25</v>
       </c>
       <c r="B1446" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C1446"/>
       <c r="D1446"/>
@@ -40897,7 +41153,7 @@
         <v>25</v>
       </c>
       <c r="B1447" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C1447"/>
       <c r="D1447"/>
@@ -40925,7 +41181,7 @@
         <v>25</v>
       </c>
       <c r="B1448" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C1448"/>
       <c r="D1448"/>
@@ -40953,7 +41209,7 @@
         <v>25</v>
       </c>
       <c r="B1449" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C1449"/>
       <c r="D1449"/>
@@ -40981,7 +41237,7 @@
         <v>26</v>
       </c>
       <c r="B1450" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C1450"/>
       <c r="D1450"/>
@@ -41009,7 +41265,7 @@
         <v>26</v>
       </c>
       <c r="B1451" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C1451"/>
       <c r="D1451"/>
@@ -41037,7 +41293,7 @@
         <v>26</v>
       </c>
       <c r="B1452" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C1452"/>
       <c r="D1452"/>
@@ -41093,7 +41349,7 @@
         <v>26</v>
       </c>
       <c r="B1454" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C1454"/>
       <c r="D1454"/>
@@ -41121,7 +41377,7 @@
         <v>26</v>
       </c>
       <c r="B1455" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C1455"/>
       <c r="D1455"/>
@@ -41149,7 +41405,7 @@
         <v>27</v>
       </c>
       <c r="B1456" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C1456"/>
       <c r="D1456"/>
@@ -41177,7 +41433,7 @@
         <v>27</v>
       </c>
       <c r="B1457" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C1457"/>
       <c r="D1457"/>
@@ -41205,7 +41461,7 @@
         <v>27</v>
       </c>
       <c r="B1458" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C1458"/>
       <c r="D1458"/>
@@ -41233,7 +41489,7 @@
         <v>27</v>
       </c>
       <c r="B1459" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C1459"/>
       <c r="D1459"/>
@@ -41261,7 +41517,7 @@
         <v>27</v>
       </c>
       <c r="B1460" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C1460"/>
       <c r="D1460"/>
@@ -41289,7 +41545,7 @@
         <v>27</v>
       </c>
       <c r="B1461" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C1461"/>
       <c r="D1461"/>
@@ -41317,7 +41573,7 @@
         <v>28</v>
       </c>
       <c r="B1462" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C1462"/>
       <c r="D1462"/>
@@ -41345,7 +41601,7 @@
         <v>28</v>
       </c>
       <c r="B1463" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C1463"/>
       <c r="D1463"/>
@@ -41373,7 +41629,7 @@
         <v>28</v>
       </c>
       <c r="B1464" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C1464"/>
       <c r="D1464"/>
@@ -41401,7 +41657,7 @@
         <v>28</v>
       </c>
       <c r="B1465" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C1465"/>
       <c r="D1465"/>
@@ -41457,7 +41713,7 @@
         <v>28</v>
       </c>
       <c r="B1467" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C1467"/>
       <c r="D1467"/>
@@ -41485,7 +41741,7 @@
         <v>29</v>
       </c>
       <c r="B1468" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C1468"/>
       <c r="D1468"/>
@@ -41513,7 +41769,7 @@
         <v>29</v>
       </c>
       <c r="B1469" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C1469"/>
       <c r="D1469"/>
@@ -41541,7 +41797,7 @@
         <v>29</v>
       </c>
       <c r="B1470" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C1470"/>
       <c r="D1470"/>
@@ -41569,7 +41825,7 @@
         <v>29</v>
       </c>
       <c r="B1471" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C1471"/>
       <c r="D1471"/>
@@ -41597,7 +41853,7 @@
         <v>29</v>
       </c>
       <c r="B1472" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C1472"/>
       <c r="D1472"/>
@@ -41625,7 +41881,7 @@
         <v>29</v>
       </c>
       <c r="B1473" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C1473"/>
       <c r="D1473"/>
@@ -41653,7 +41909,7 @@
         <v>30</v>
       </c>
       <c r="B1474" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C1474"/>
       <c r="D1474"/>
@@ -41681,7 +41937,7 @@
         <v>30</v>
       </c>
       <c r="B1475" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C1475"/>
       <c r="D1475"/>
@@ -41709,7 +41965,7 @@
         <v>30</v>
       </c>
       <c r="B1476" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C1476"/>
       <c r="D1476"/>
@@ -41737,7 +41993,7 @@
         <v>30</v>
       </c>
       <c r="B1477" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C1477"/>
       <c r="D1477"/>
@@ -41765,7 +42021,7 @@
         <v>30</v>
       </c>
       <c r="B1478" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C1478"/>
       <c r="D1478"/>
@@ -41793,7 +42049,7 @@
         <v>30</v>
       </c>
       <c r="B1479" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C1479"/>
       <c r="D1479"/>
@@ -41821,7 +42077,7 @@
         <v>31</v>
       </c>
       <c r="B1480" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C1480"/>
       <c r="D1480"/>
@@ -41849,7 +42105,7 @@
         <v>31</v>
       </c>
       <c r="B1481" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C1481"/>
       <c r="D1481"/>
@@ -41877,7 +42133,7 @@
         <v>31</v>
       </c>
       <c r="B1482" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C1482"/>
       <c r="D1482"/>
@@ -41905,7 +42161,7 @@
         <v>31</v>
       </c>
       <c r="B1483" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C1483"/>
       <c r="D1483"/>
@@ -41961,7 +42217,7 @@
         <v>31</v>
       </c>
       <c r="B1485" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C1485"/>
       <c r="D1485"/>
@@ -41989,7 +42245,7 @@
         <v>32</v>
       </c>
       <c r="B1486" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C1486"/>
       <c r="D1486"/>
@@ -42017,7 +42273,7 @@
         <v>32</v>
       </c>
       <c r="B1487" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C1487"/>
       <c r="D1487"/>
@@ -42073,7 +42329,7 @@
         <v>32</v>
       </c>
       <c r="B1489" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C1489"/>
       <c r="D1489"/>
@@ -42129,7 +42385,7 @@
         <v>32</v>
       </c>
       <c r="B1491" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C1491"/>
       <c r="D1491"/>
@@ -42157,7 +42413,7 @@
         <v>22</v>
       </c>
       <c r="B1492" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C1492"/>
       <c r="D1492"/>
@@ -42185,7 +42441,7 @@
         <v>22</v>
       </c>
       <c r="B1493" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C1493"/>
       <c r="D1493"/>
@@ -42213,7 +42469,7 @@
         <v>22</v>
       </c>
       <c r="B1494" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C1494"/>
       <c r="D1494"/>
@@ -42269,7 +42525,7 @@
         <v>22</v>
       </c>
       <c r="B1496" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C1496"/>
       <c r="D1496"/>
@@ -42297,7 +42553,7 @@
         <v>22</v>
       </c>
       <c r="B1497" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C1497"/>
       <c r="D1497"/>
@@ -42325,7 +42581,7 @@
         <v>33</v>
       </c>
       <c r="B1498" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C1498"/>
       <c r="D1498"/>
@@ -42353,7 +42609,7 @@
         <v>33</v>
       </c>
       <c r="B1499" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C1499"/>
       <c r="D1499"/>
@@ -42381,7 +42637,7 @@
         <v>33</v>
       </c>
       <c r="B1500" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C1500"/>
       <c r="D1500"/>
@@ -42409,7 +42665,7 @@
         <v>33</v>
       </c>
       <c r="B1501" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C1501"/>
       <c r="D1501"/>
@@ -42437,7 +42693,7 @@
         <v>33</v>
       </c>
       <c r="B1502" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C1502"/>
       <c r="D1502"/>
@@ -42465,7 +42721,7 @@
         <v>33</v>
       </c>
       <c r="B1503" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C1503"/>
       <c r="D1503"/>
@@ -42493,7 +42749,7 @@
         <v>34</v>
       </c>
       <c r="B1504" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C1504"/>
       <c r="D1504"/>
@@ -42521,7 +42777,7 @@
         <v>34</v>
       </c>
       <c r="B1505" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C1505"/>
       <c r="D1505"/>
@@ -42549,7 +42805,7 @@
         <v>34</v>
       </c>
       <c r="B1506" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C1506"/>
       <c r="D1506"/>
@@ -42577,7 +42833,7 @@
         <v>34</v>
       </c>
       <c r="B1507" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C1507"/>
       <c r="D1507"/>
@@ -42605,7 +42861,7 @@
         <v>34</v>
       </c>
       <c r="B1508" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C1508"/>
       <c r="D1508"/>
@@ -42633,7 +42889,7 @@
         <v>34</v>
       </c>
       <c r="B1509" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C1509"/>
       <c r="D1509"/>
@@ -42661,7 +42917,7 @@
         <v>35</v>
       </c>
       <c r="B1510" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C1510"/>
       <c r="D1510"/>
@@ -42689,7 +42945,7 @@
         <v>35</v>
       </c>
       <c r="B1511" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C1511"/>
       <c r="D1511"/>
@@ -42717,7 +42973,7 @@
         <v>35</v>
       </c>
       <c r="B1512" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C1512"/>
       <c r="D1512"/>
@@ -42745,7 +43001,7 @@
         <v>35</v>
       </c>
       <c r="B1513" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C1513"/>
       <c r="D1513"/>
@@ -42773,7 +43029,7 @@
         <v>35</v>
       </c>
       <c r="B1514" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C1514"/>
       <c r="D1514"/>
@@ -42801,7 +43057,7 @@
         <v>35</v>
       </c>
       <c r="B1515" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C1515"/>
       <c r="D1515"/>
@@ -42829,7 +43085,7 @@
         <v>36</v>
       </c>
       <c r="B1516" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C1516"/>
       <c r="D1516"/>
@@ -42857,7 +43113,7 @@
         <v>36</v>
       </c>
       <c r="B1517" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C1517"/>
       <c r="D1517"/>
@@ -42885,7 +43141,7 @@
         <v>36</v>
       </c>
       <c r="B1518" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C1518"/>
       <c r="D1518"/>
@@ -42941,7 +43197,7 @@
         <v>36</v>
       </c>
       <c r="B1520" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C1520"/>
       <c r="D1520"/>
@@ -42969,7 +43225,7 @@
         <v>36</v>
       </c>
       <c r="B1521" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C1521"/>
       <c r="D1521"/>
@@ -42992,454 +43248,6 @@
       </c>
       <c r="T1521"/>
     </row>
-    <row r="1522">
-      <c r="A1522" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1522" t="s">
-        <v>62</v>
-      </c>
-      <c r="C1522"/>
-      <c r="D1522"/>
-      <c r="E1522"/>
-      <c r="F1522"/>
-      <c r="G1522"/>
-      <c r="H1522"/>
-      <c r="I1522"/>
-      <c r="J1522"/>
-      <c r="K1522"/>
-      <c r="L1522"/>
-      <c r="M1522"/>
-      <c r="N1522"/>
-      <c r="O1522"/>
-      <c r="P1522"/>
-      <c r="Q1522"/>
-      <c r="R1522"/>
-      <c r="S1522"/>
-      <c r="T1522" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="1523">
-      <c r="A1523" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1523" t="s">
-        <v>62</v>
-      </c>
-      <c r="C1523"/>
-      <c r="D1523"/>
-      <c r="E1523"/>
-      <c r="F1523"/>
-      <c r="G1523"/>
-      <c r="H1523"/>
-      <c r="I1523"/>
-      <c r="J1523"/>
-      <c r="K1523"/>
-      <c r="L1523"/>
-      <c r="M1523"/>
-      <c r="N1523"/>
-      <c r="O1523"/>
-      <c r="P1523"/>
-      <c r="Q1523"/>
-      <c r="R1523"/>
-      <c r="S1523"/>
-      <c r="T1523" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="1524">
-      <c r="A1524" t="s">
-        <v>24</v>
-      </c>
-      <c r="B1524" t="s">
-        <v>62</v>
-      </c>
-      <c r="C1524"/>
-      <c r="D1524"/>
-      <c r="E1524"/>
-      <c r="F1524"/>
-      <c r="G1524"/>
-      <c r="H1524"/>
-      <c r="I1524"/>
-      <c r="J1524"/>
-      <c r="K1524"/>
-      <c r="L1524"/>
-      <c r="M1524"/>
-      <c r="N1524"/>
-      <c r="O1524"/>
-      <c r="P1524"/>
-      <c r="Q1524"/>
-      <c r="R1524"/>
-      <c r="S1524"/>
-      <c r="T1524" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="1525">
-      <c r="A1525" t="s">
-        <v>25</v>
-      </c>
-      <c r="B1525" t="s">
-        <v>62</v>
-      </c>
-      <c r="C1525"/>
-      <c r="D1525"/>
-      <c r="E1525"/>
-      <c r="F1525"/>
-      <c r="G1525"/>
-      <c r="H1525"/>
-      <c r="I1525"/>
-      <c r="J1525"/>
-      <c r="K1525"/>
-      <c r="L1525"/>
-      <c r="M1525"/>
-      <c r="N1525"/>
-      <c r="O1525"/>
-      <c r="P1525"/>
-      <c r="Q1525"/>
-      <c r="R1525"/>
-      <c r="S1525"/>
-      <c r="T1525" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="1526">
-      <c r="A1526" t="s">
-        <v>26</v>
-      </c>
-      <c r="B1526" t="s">
-        <v>62</v>
-      </c>
-      <c r="C1526"/>
-      <c r="D1526"/>
-      <c r="E1526"/>
-      <c r="F1526"/>
-      <c r="G1526"/>
-      <c r="H1526"/>
-      <c r="I1526"/>
-      <c r="J1526"/>
-      <c r="K1526"/>
-      <c r="L1526"/>
-      <c r="M1526"/>
-      <c r="N1526"/>
-      <c r="O1526"/>
-      <c r="P1526"/>
-      <c r="Q1526"/>
-      <c r="R1526"/>
-      <c r="S1526"/>
-      <c r="T1526" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="1527">
-      <c r="A1527" t="s">
-        <v>27</v>
-      </c>
-      <c r="B1527" t="s">
-        <v>62</v>
-      </c>
-      <c r="C1527"/>
-      <c r="D1527"/>
-      <c r="E1527"/>
-      <c r="F1527"/>
-      <c r="G1527"/>
-      <c r="H1527"/>
-      <c r="I1527"/>
-      <c r="J1527"/>
-      <c r="K1527"/>
-      <c r="L1527"/>
-      <c r="M1527"/>
-      <c r="N1527"/>
-      <c r="O1527"/>
-      <c r="P1527"/>
-      <c r="Q1527"/>
-      <c r="R1527"/>
-      <c r="S1527"/>
-      <c r="T1527" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="1528">
-      <c r="A1528" t="s">
-        <v>28</v>
-      </c>
-      <c r="B1528" t="s">
-        <v>62</v>
-      </c>
-      <c r="C1528"/>
-      <c r="D1528"/>
-      <c r="E1528"/>
-      <c r="F1528"/>
-      <c r="G1528"/>
-      <c r="H1528"/>
-      <c r="I1528"/>
-      <c r="J1528"/>
-      <c r="K1528"/>
-      <c r="L1528"/>
-      <c r="M1528"/>
-      <c r="N1528"/>
-      <c r="O1528"/>
-      <c r="P1528"/>
-      <c r="Q1528"/>
-      <c r="R1528"/>
-      <c r="S1528"/>
-      <c r="T1528" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="1529">
-      <c r="A1529" t="s">
-        <v>29</v>
-      </c>
-      <c r="B1529" t="s">
-        <v>62</v>
-      </c>
-      <c r="C1529"/>
-      <c r="D1529"/>
-      <c r="E1529"/>
-      <c r="F1529"/>
-      <c r="G1529"/>
-      <c r="H1529"/>
-      <c r="I1529"/>
-      <c r="J1529"/>
-      <c r="K1529"/>
-      <c r="L1529"/>
-      <c r="M1529"/>
-      <c r="N1529"/>
-      <c r="O1529"/>
-      <c r="P1529"/>
-      <c r="Q1529"/>
-      <c r="R1529"/>
-      <c r="S1529"/>
-      <c r="T1529" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="1530">
-      <c r="A1530" t="s">
-        <v>30</v>
-      </c>
-      <c r="B1530" t="s">
-        <v>62</v>
-      </c>
-      <c r="C1530"/>
-      <c r="D1530"/>
-      <c r="E1530"/>
-      <c r="F1530"/>
-      <c r="G1530"/>
-      <c r="H1530"/>
-      <c r="I1530"/>
-      <c r="J1530"/>
-      <c r="K1530"/>
-      <c r="L1530"/>
-      <c r="M1530"/>
-      <c r="N1530"/>
-      <c r="O1530"/>
-      <c r="P1530"/>
-      <c r="Q1530"/>
-      <c r="R1530"/>
-      <c r="S1530"/>
-      <c r="T1530" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="1531">
-      <c r="A1531" t="s">
-        <v>31</v>
-      </c>
-      <c r="B1531" t="s">
-        <v>62</v>
-      </c>
-      <c r="C1531"/>
-      <c r="D1531"/>
-      <c r="E1531"/>
-      <c r="F1531"/>
-      <c r="G1531"/>
-      <c r="H1531"/>
-      <c r="I1531"/>
-      <c r="J1531"/>
-      <c r="K1531"/>
-      <c r="L1531"/>
-      <c r="M1531"/>
-      <c r="N1531"/>
-      <c r="O1531"/>
-      <c r="P1531"/>
-      <c r="Q1531"/>
-      <c r="R1531"/>
-      <c r="S1531"/>
-      <c r="T1531" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="1532">
-      <c r="A1532" t="s">
-        <v>32</v>
-      </c>
-      <c r="B1532" t="s">
-        <v>62</v>
-      </c>
-      <c r="C1532"/>
-      <c r="D1532"/>
-      <c r="E1532"/>
-      <c r="F1532"/>
-      <c r="G1532"/>
-      <c r="H1532"/>
-      <c r="I1532"/>
-      <c r="J1532"/>
-      <c r="K1532"/>
-      <c r="L1532"/>
-      <c r="M1532"/>
-      <c r="N1532"/>
-      <c r="O1532"/>
-      <c r="P1532"/>
-      <c r="Q1532"/>
-      <c r="R1532"/>
-      <c r="S1532"/>
-      <c r="T1532" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="1533">
-      <c r="A1533" t="s">
-        <v>22</v>
-      </c>
-      <c r="B1533" t="s">
-        <v>62</v>
-      </c>
-      <c r="C1533"/>
-      <c r="D1533"/>
-      <c r="E1533"/>
-      <c r="F1533"/>
-      <c r="G1533"/>
-      <c r="H1533"/>
-      <c r="I1533"/>
-      <c r="J1533"/>
-      <c r="K1533"/>
-      <c r="L1533"/>
-      <c r="M1533"/>
-      <c r="N1533"/>
-      <c r="O1533"/>
-      <c r="P1533"/>
-      <c r="Q1533"/>
-      <c r="R1533"/>
-      <c r="S1533"/>
-      <c r="T1533" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="1534">
-      <c r="A1534" t="s">
-        <v>33</v>
-      </c>
-      <c r="B1534" t="s">
-        <v>62</v>
-      </c>
-      <c r="C1534"/>
-      <c r="D1534"/>
-      <c r="E1534"/>
-      <c r="F1534"/>
-      <c r="G1534"/>
-      <c r="H1534"/>
-      <c r="I1534"/>
-      <c r="J1534"/>
-      <c r="K1534"/>
-      <c r="L1534"/>
-      <c r="M1534"/>
-      <c r="N1534"/>
-      <c r="O1534"/>
-      <c r="P1534"/>
-      <c r="Q1534"/>
-      <c r="R1534"/>
-      <c r="S1534"/>
-      <c r="T1534" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="1535">
-      <c r="A1535" t="s">
-        <v>34</v>
-      </c>
-      <c r="B1535" t="s">
-        <v>62</v>
-      </c>
-      <c r="C1535"/>
-      <c r="D1535"/>
-      <c r="E1535"/>
-      <c r="F1535"/>
-      <c r="G1535"/>
-      <c r="H1535"/>
-      <c r="I1535"/>
-      <c r="J1535"/>
-      <c r="K1535"/>
-      <c r="L1535"/>
-      <c r="M1535"/>
-      <c r="N1535"/>
-      <c r="O1535"/>
-      <c r="P1535"/>
-      <c r="Q1535"/>
-      <c r="R1535"/>
-      <c r="S1535"/>
-      <c r="T1535" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="1536">
-      <c r="A1536" t="s">
-        <v>35</v>
-      </c>
-      <c r="B1536" t="s">
-        <v>62</v>
-      </c>
-      <c r="C1536"/>
-      <c r="D1536"/>
-      <c r="E1536"/>
-      <c r="F1536"/>
-      <c r="G1536"/>
-      <c r="H1536"/>
-      <c r="I1536"/>
-      <c r="J1536"/>
-      <c r="K1536"/>
-      <c r="L1536"/>
-      <c r="M1536"/>
-      <c r="N1536"/>
-      <c r="O1536"/>
-      <c r="P1536"/>
-      <c r="Q1536"/>
-      <c r="R1536"/>
-      <c r="S1536"/>
-      <c r="T1536" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="1537">
-      <c r="A1537" t="s">
-        <v>36</v>
-      </c>
-      <c r="B1537" t="s">
-        <v>62</v>
-      </c>
-      <c r="C1537"/>
-      <c r="D1537"/>
-      <c r="E1537"/>
-      <c r="F1537"/>
-      <c r="G1537"/>
-      <c r="H1537"/>
-      <c r="I1537"/>
-      <c r="J1537"/>
-      <c r="K1537"/>
-      <c r="L1537"/>
-      <c r="M1537"/>
-      <c r="N1537"/>
-      <c r="O1537"/>
-      <c r="P1537"/>
-      <c r="Q1537"/>
-      <c r="R1537"/>
-      <c r="S1537"/>
-      <c r="T1537" t="s">
-        <v>115</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
